--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-18T12:02:45+00:00</t>
+    <t>2023-04-24T21:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T20:59:20+00:00</t>
+    <t>2023-04-30T21:23:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T21:23:00+00:00</t>
+    <t>2023-05-05T00:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:13:03+00:00</t>
+    <t>2023-11-30T13:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T13:40:49+00:00</t>
+    <t>2023-11-30T14:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2420,7 +2420,7 @@
     <t>SCTCode</t>
   </si>
   <si>
-    <t>http://hl7.dk/fhir/core/ValueSet/TechniqesSCTCodes</t>
+    <t>http://hl7.dk/fhir/core/ValueSet/dk-core-TechniquesSCTCodes</t>
   </si>
   <si>
     <t>Observation.method.coding:SCTCode.id</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T14:55:40+00:00</t>
+    <t>2023-12-01T12:31:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:28:26+00:00</t>
+    <t>2023-12-19T10:34:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:34:37+00:00</t>
+    <t>2024-01-06T18:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:06+00:00</t>
+    <t>2024-01-08T22:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24977" uniqueCount="1567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26305" uniqueCount="1652">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-19T10:43:29+00:00</t>
+    <t>2024-04-03T07:46:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1329,7 +1329,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|RelatedPerson)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -2688,7 +2688,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|PractitionerRole|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -4225,10 +4225,7 @@
     <t>Used to determine which contact person is the most relevant to approach, depending on circumstances.</t>
   </si>
   <si>
-    <t>The nature of the relationship between a patient and a contact person for that patient.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship</t>
+    <t>http://hl7.dk/fhir/core/ValueSet/dk-core-RelatedPersonRelationshipTypes</t>
   </si>
   <si>
     <t>Patient.contact.name</t>
@@ -4858,6 +4855,264 @@
   </si>
   <si>
     <t>http://medcomfhir.dk/ig/terminology/CodeSystem/MedComProducentID</t>
+  </si>
+  <si>
+    <t>dk-core-related-person</t>
+  </si>
+  <si>
+    <t>http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person</t>
+  </si>
+  <si>
+    <t>DkCoreRelatedPerson</t>
+  </si>
+  <si>
+    <t>Danish Core Related Person Profile</t>
+  </si>
+  <si>
+    <t>HL7 Denmark core profile for a related person</t>
+  </si>
+  <si>
+    <t>RelatedPerson</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/RelatedPerson</t>
+  </si>
+  <si>
+    <t>A person that is related to a patient, but who is not a direct target of care</t>
+  </si>
+  <si>
+    <t>Information about a person that is involved in the care for a patient, but who is not the target of healthcare, nor has a formal responsibility in the care process.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.meta</t>
+  </si>
+  <si>
+    <t>RelatedPerson.implicitRules</t>
+  </si>
+  <si>
+    <t>RelatedPerson.language</t>
+  </si>
+  <si>
+    <t>RelatedPerson.text</t>
+  </si>
+  <si>
+    <t>RelatedPerson.contained</t>
+  </si>
+  <si>
+    <t>RelatedPerson.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.modifierExtension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.identifier</t>
+  </si>
+  <si>
+    <t>A human identifier for this person</t>
+  </si>
+  <si>
+    <t>Identifier for a person within a particular scope.</t>
+  </si>
+  <si>
+    <t>People are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the patient. Examples are national person identifier and local identifier.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.identifier:cpr</t>
+  </si>
+  <si>
+    <t>RelatedPerson.identifier:x-ecpr</t>
+  </si>
+  <si>
+    <t>RelatedPerson.identifier:d-ecpr</t>
+  </si>
+  <si>
+    <t>RelatedPerson.active</t>
+  </si>
+  <si>
+    <t>Whether this related person's record is in active use</t>
+  </si>
+  <si>
+    <t>Whether this related person record is in active use.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
+  </si>
+  <si>
+    <t>Need to be able to mark a related person record as not to be used, such as if it was created in error.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.patient</t>
+  </si>
+  <si>
+    <t>The patient this person is related to</t>
+  </si>
+  <si>
+    <t>The patient this person is related to.</t>
+  </si>
+  <si>
+    <t>We need to know which patient this RelatedPerson is related to.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship</t>
+  </si>
+  <si>
+    <t>The nature of the relationship</t>
+  </si>
+  <si>
+    <t>The nature of the relationship between a patient and the related person.</t>
+  </si>
+  <si>
+    <t>We need to know the relationship with the patient since it influences the interpretation of the information attributed to this person.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name</t>
+  </si>
+  <si>
+    <t>A name associated with the person</t>
+  </si>
+  <si>
+    <t>A name associated with the person.</t>
+  </si>
+  <si>
+    <t>Related persons need to be identified by name, but it is uncommon to need details about multiple other names for that person.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name:official</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name:official.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name:official.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name:official.use</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name.use</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name:official.text</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name.text</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name:official.family</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name.family</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name:official.given</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name.given</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name:official.prefix</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name.prefix</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name:official.suffix</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name.suffix</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name:official.period</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name.period</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom</t>
+  </si>
+  <si>
+    <t>Person may have multiple ways to be contacted with different uses or applicable periods.  May need to have options for contacting the person urgently, and also to help with identification.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.gender</t>
+  </si>
+  <si>
+    <t>Needed for identification of the person, in combination with (at least) name and birth date.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.birthDate</t>
+  </si>
+  <si>
+    <t>The date on which the related person was born</t>
+  </si>
+  <si>
+    <t>The date on which the related person was born.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.address</t>
+  </si>
+  <si>
+    <t>Address where the related person can be contacted or visited</t>
+  </si>
+  <si>
+    <t>Address where the related person can be contacted or visited.</t>
+  </si>
+  <si>
+    <t>Need to keep track where the related person can be contacted per postal mail or visited.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.photo</t>
+  </si>
+  <si>
+    <t>Many EHR systems have the capability to capture an image of persons. Fits with newer social media usage too.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.period</t>
+  </si>
+  <si>
+    <t>Period of time that this relationship is considered valid</t>
+  </si>
+  <si>
+    <t>The period of time during which this relationship is or was active. If there are no dates defined, then the interval is unknown.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.communication</t>
+  </si>
+  <si>
+    <t>A language which may be used to communicate with about the patient's health</t>
+  </si>
+  <si>
+    <t>A language which may be used to communicate with about the patient's health.</t>
+  </si>
+  <si>
+    <t>If no language is specified, this *implies* that the default local language is spoken.  If you need to convey proficiency for multiple modes, then you need multiple RelatedPerson.Communication associations.   If the RelatedPerson does not speak the default local language, then the Interpreter Required Standard can be used to explicitly declare that an interpreter is required.</t>
+  </si>
+  <si>
+    <t>If a related person does not speak the local language, interpreters may be required, so languages spoken and proficiency is an important things to keep track of both for patient and other persons of interest.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.communication.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.communication.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.communication.modifierExtension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.communication.language</t>
+  </si>
+  <si>
+    <t>RelatedPerson.communication.preferred</t>
   </si>
   <si>
     <t>dk-core-sor-identifier</t>
@@ -5035,7 +5290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B405"/>
+  <dimension ref="A1:B426"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -7533,7 +7788,7 @@
         <v>2</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="324">
@@ -7541,7 +7796,7 @@
         <v>4</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="325">
@@ -7557,7 +7812,7 @@
         <v>8</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="327">
@@ -7565,7 +7820,7 @@
         <v>9</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="328">
@@ -7619,7 +7874,7 @@
         <v>21</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>1458</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="335">
@@ -7655,7 +7910,7 @@
         <v>29</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>1459</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="340">
@@ -7663,7 +7918,7 @@
         <v>31</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="341">
@@ -7695,7 +7950,7 @@
         <v>2</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="345">
@@ -7703,7 +7958,7 @@
         <v>4</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>1548</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="346">
@@ -7719,7 +7974,7 @@
         <v>8</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="348">
@@ -7727,7 +7982,7 @@
         <v>9</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="349">
@@ -7781,7 +8036,7 @@
         <v>21</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="356">
@@ -7857,7 +8112,7 @@
         <v>2</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="366">
@@ -7865,7 +8120,7 @@
         <v>4</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>1554</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="367">
@@ -7881,7 +8136,7 @@
         <v>8</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="369">
@@ -7889,7 +8144,7 @@
         <v>9</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>1556</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="370">
@@ -7943,7 +8198,7 @@
         <v>21</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>1557</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="377">
@@ -7971,7 +8226,7 @@
         <v>27</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>28</v>
+        <v>192</v>
       </c>
     </row>
     <row r="381">
@@ -7979,7 +8234,7 @@
         <v>29</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>142</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="382">
@@ -7987,7 +8242,7 @@
         <v>31</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>143</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="383">
@@ -8019,7 +8274,7 @@
         <v>2</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>1560</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="387">
@@ -8027,7 +8282,7 @@
         <v>4</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>1561</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="388">
@@ -8043,7 +8298,7 @@
         <v>8</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>1562</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="390">
@@ -8051,7 +8306,7 @@
         <v>9</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>1563</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="391">
@@ -8105,7 +8360,7 @@
         <v>21</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>1564</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="398">
@@ -8165,6 +8420,168 @@
         <v>35</v>
       </c>
       <c r="B405" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B406" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B407" t="s" s="2">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B408" t="s" s="2">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="B409" t="s" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="B410" t="s" s="2">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B411" t="s" s="2">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="B412" t="s" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="B413" s="2"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B414" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B415" t="s" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B416" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B417" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B418" t="s" s="2">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B419" s="2"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B420" s="2"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B421" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B422" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B423" t="s" s="2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B424" t="s" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B425" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B426" t="s" s="2">
         <v>36</v>
       </c>
     </row>
@@ -8175,7 +8592,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK729"/>
+  <dimension ref="A1:AK768"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.99609375" customWidth="true" bestFit="true"/>
@@ -8204,7 +8621,7 @@
     <col min="24" max="24" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="62.0" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="67.6640625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="23.2734375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="91.359375" customWidth="true" bestFit="true"/>
@@ -75743,11 +76160,9 @@
       <c r="Y641" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="Z641" t="s" s="2">
+      <c r="Z641" s="2"/>
+      <c r="AA641" t="s" s="2">
         <v>1350</v>
-      </c>
-      <c r="AA641" t="s" s="2">
-        <v>1351</v>
       </c>
       <c r="AB641" t="s" s="2">
         <v>75</v>
@@ -75785,10 +76200,10 @@
         <v>1123</v>
       </c>
       <c r="B642" t="s" s="2">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="C642" t="s" s="2">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D642" s="2"/>
       <c r="E642" t="s" s="2">
@@ -75814,14 +76229,14 @@
         <v>1106</v>
       </c>
       <c r="M642" t="s" s="2">
+        <v>1352</v>
+      </c>
+      <c r="N642" t="s" s="2">
         <v>1353</v>
-      </c>
-      <c r="N642" t="s" s="2">
-        <v>1354</v>
       </c>
       <c r="O642" s="2"/>
       <c r="P642" t="s" s="2">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="Q642" t="s" s="2">
         <v>75</v>
@@ -75870,7 +76285,7 @@
         <v>75</v>
       </c>
       <c r="AG642" t="s" s="2">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="AH642" t="s" s="2">
         <v>76</v>
@@ -75890,10 +76305,10 @@
         <v>1123</v>
       </c>
       <c r="B643" t="s" s="2">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C643" t="s" s="2">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D643" s="2"/>
       <c r="E643" t="s" s="2">
@@ -75919,13 +76334,13 @@
         <v>1072</v>
       </c>
       <c r="M643" t="s" s="2">
+        <v>1356</v>
+      </c>
+      <c r="N643" t="s" s="2">
         <v>1357</v>
       </c>
-      <c r="N643" t="s" s="2">
+      <c r="O643" t="s" s="2">
         <v>1358</v>
-      </c>
-      <c r="O643" t="s" s="2">
-        <v>1359</v>
       </c>
       <c r="P643" t="s" s="2">
         <v>1113</v>
@@ -75977,7 +76392,7 @@
         <v>75</v>
       </c>
       <c r="AG643" t="s" s="2">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="AH643" t="s" s="2">
         <v>76</v>
@@ -75997,10 +76412,10 @@
         <v>1123</v>
       </c>
       <c r="B644" t="s" s="2">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="C644" t="s" s="2">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D644" s="2"/>
       <c r="E644" t="s" s="2">
@@ -76026,14 +76441,14 @@
         <v>1080</v>
       </c>
       <c r="M644" t="s" s="2">
+        <v>1360</v>
+      </c>
+      <c r="N644" t="s" s="2">
         <v>1361</v>
-      </c>
-      <c r="N644" t="s" s="2">
-        <v>1362</v>
       </c>
       <c r="O644" s="2"/>
       <c r="P644" t="s" s="2">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="Q644" t="s" s="2">
         <v>75</v>
@@ -76082,7 +76497,7 @@
         <v>75</v>
       </c>
       <c r="AG644" t="s" s="2">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="AH644" t="s" s="2">
         <v>76</v>
@@ -76102,10 +76517,10 @@
         <v>1123</v>
       </c>
       <c r="B645" t="s" s="2">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="C645" t="s" s="2">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="D645" s="2"/>
       <c r="E645" t="s" s="2">
@@ -76134,11 +76549,11 @@
         <v>1226</v>
       </c>
       <c r="N645" t="s" s="2">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="O645" s="2"/>
       <c r="P645" t="s" s="2">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="Q645" t="s" s="2">
         <v>75</v>
@@ -76187,7 +76602,7 @@
         <v>75</v>
       </c>
       <c r="AG645" t="s" s="2">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="AH645" t="s" s="2">
         <v>76</v>
@@ -76207,10 +76622,10 @@
         <v>1123</v>
       </c>
       <c r="B646" t="s" s="2">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="C646" t="s" s="2">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D646" s="2"/>
       <c r="E646" t="s" s="2">
@@ -76236,14 +76651,14 @@
         <v>183</v>
       </c>
       <c r="M646" t="s" s="2">
+        <v>1367</v>
+      </c>
+      <c r="N646" t="s" s="2">
         <v>1368</v>
-      </c>
-      <c r="N646" t="s" s="2">
-        <v>1369</v>
       </c>
       <c r="O646" s="2"/>
       <c r="P646" t="s" s="2">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="Q646" t="s" s="2">
         <v>75</v>
@@ -76292,7 +76707,7 @@
         <v>75</v>
       </c>
       <c r="AG646" t="s" s="2">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="AH646" t="s" s="2">
         <v>76</v>
@@ -76301,7 +76716,7 @@
         <v>82</v>
       </c>
       <c r="AJ646" t="s" s="2">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="AK646" t="s" s="2">
         <v>103</v>
@@ -76312,10 +76727,10 @@
         <v>1123</v>
       </c>
       <c r="B647" t="s" s="2">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="C647" t="s" s="2">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="D647" s="2"/>
       <c r="E647" t="s" s="2">
@@ -76341,10 +76756,10 @@
         <v>179</v>
       </c>
       <c r="M647" t="s" s="2">
+        <v>1372</v>
+      </c>
+      <c r="N647" t="s" s="2">
         <v>1373</v>
-      </c>
-      <c r="N647" t="s" s="2">
-        <v>1374</v>
       </c>
       <c r="O647" s="2"/>
       <c r="P647" s="2"/>
@@ -76395,7 +76810,7 @@
         <v>75</v>
       </c>
       <c r="AG647" t="s" s="2">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="AH647" t="s" s="2">
         <v>76</v>
@@ -76415,10 +76830,10 @@
         <v>1123</v>
       </c>
       <c r="B648" t="s" s="2">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="C648" t="s" s="2">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="D648" s="2"/>
       <c r="E648" t="s" s="2">
@@ -76444,16 +76859,16 @@
         <v>549</v>
       </c>
       <c r="M648" t="s" s="2">
+        <v>1375</v>
+      </c>
+      <c r="N648" t="s" s="2">
         <v>1376</v>
       </c>
-      <c r="N648" t="s" s="2">
+      <c r="O648" t="s" s="2">
         <v>1377</v>
       </c>
-      <c r="O648" t="s" s="2">
+      <c r="P648" t="s" s="2">
         <v>1378</v>
-      </c>
-      <c r="P648" t="s" s="2">
-        <v>1379</v>
       </c>
       <c r="Q648" t="s" s="2">
         <v>75</v>
@@ -76502,7 +76917,7 @@
         <v>75</v>
       </c>
       <c r="AG648" t="s" s="2">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="AH648" t="s" s="2">
         <v>76</v>
@@ -76522,10 +76937,10 @@
         <v>1123</v>
       </c>
       <c r="B649" t="s" s="2">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="C649" t="s" s="2">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="D649" s="2"/>
       <c r="E649" t="s" s="2">
@@ -76625,10 +77040,10 @@
         <v>1123</v>
       </c>
       <c r="B650" t="s" s="2">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="C650" t="s" s="2">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D650" s="2"/>
       <c r="E650" t="s" s="2">
@@ -76730,10 +77145,10 @@
         <v>1123</v>
       </c>
       <c r="B651" t="s" s="2">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="C651" t="s" s="2">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D651" s="2"/>
       <c r="E651" t="s" s="2">
@@ -76837,10 +77252,10 @@
         <v>1123</v>
       </c>
       <c r="B652" t="s" s="2">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="C652" t="s" s="2">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="D652" s="2"/>
       <c r="E652" t="s" s="2">
@@ -76866,16 +77281,16 @@
         <v>114</v>
       </c>
       <c r="M652" t="s" s="2">
+        <v>1383</v>
+      </c>
+      <c r="N652" t="s" s="2">
         <v>1384</v>
       </c>
-      <c r="N652" t="s" s="2">
+      <c r="O652" t="s" s="2">
         <v>1385</v>
       </c>
-      <c r="O652" t="s" s="2">
+      <c r="P652" t="s" s="2">
         <v>1386</v>
-      </c>
-      <c r="P652" t="s" s="2">
-        <v>1387</v>
       </c>
       <c r="Q652" t="s" s="2">
         <v>75</v>
@@ -76924,7 +77339,7 @@
         <v>75</v>
       </c>
       <c r="AG652" t="s" s="2">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="AH652" t="s" s="2">
         <v>82</v>
@@ -76944,10 +77359,10 @@
         <v>1123</v>
       </c>
       <c r="B653" t="s" s="2">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="C653" t="s" s="2">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="D653" s="2"/>
       <c r="E653" t="s" s="2">
@@ -76973,16 +77388,16 @@
         <v>327</v>
       </c>
       <c r="M653" t="s" s="2">
+        <v>1388</v>
+      </c>
+      <c r="N653" t="s" s="2">
         <v>1389</v>
       </c>
-      <c r="N653" t="s" s="2">
+      <c r="O653" t="s" s="2">
         <v>1390</v>
       </c>
-      <c r="O653" t="s" s="2">
+      <c r="P653" t="s" s="2">
         <v>1391</v>
-      </c>
-      <c r="P653" t="s" s="2">
-        <v>1392</v>
       </c>
       <c r="Q653" t="s" s="2">
         <v>75</v>
@@ -77031,7 +77446,7 @@
         <v>75</v>
       </c>
       <c r="AG653" t="s" s="2">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="AH653" t="s" s="2">
         <v>76</v>
@@ -77051,14 +77466,14 @@
         <v>1123</v>
       </c>
       <c r="B654" t="s" s="2">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="C654" t="s" s="2">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="D654" s="2"/>
       <c r="E654" t="s" s="2">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="F654" s="2"/>
       <c r="G654" t="s" s="2">
@@ -77077,16 +77492,16 @@
         <v>75</v>
       </c>
       <c r="L654" t="s" s="2">
+        <v>1394</v>
+      </c>
+      <c r="M654" t="s" s="2">
         <v>1395</v>
       </c>
-      <c r="M654" t="s" s="2">
+      <c r="N654" t="s" s="2">
         <v>1396</v>
       </c>
-      <c r="N654" t="s" s="2">
+      <c r="O654" t="s" s="2">
         <v>1397</v>
-      </c>
-      <c r="O654" t="s" s="2">
-        <v>1398</v>
       </c>
       <c r="P654" s="2"/>
       <c r="Q654" t="s" s="2">
@@ -77124,7 +77539,7 @@
         <v>75</v>
       </c>
       <c r="AC654" t="s" s="2">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="AD654" s="2"/>
       <c r="AE654" t="s" s="2">
@@ -77134,7 +77549,7 @@
         <v>92</v>
       </c>
       <c r="AG654" t="s" s="2">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="AH654" t="s" s="2">
         <v>76</v>
@@ -77154,16 +77569,16 @@
         <v>1123</v>
       </c>
       <c r="B655" t="s" s="2">
+        <v>1399</v>
+      </c>
+      <c r="C655" t="s" s="2">
+        <v>1392</v>
+      </c>
+      <c r="D655" t="s" s="2">
         <v>1400</v>
       </c>
-      <c r="C655" t="s" s="2">
+      <c r="E655" t="s" s="2">
         <v>1393</v>
-      </c>
-      <c r="D655" t="s" s="2">
-        <v>1401</v>
-      </c>
-      <c r="E655" t="s" s="2">
-        <v>1394</v>
       </c>
       <c r="F655" s="2"/>
       <c r="G655" t="s" s="2">
@@ -77182,16 +77597,16 @@
         <v>75</v>
       </c>
       <c r="L655" t="s" s="2">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="M655" t="s" s="2">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="N655" t="s" s="2">
+        <v>1396</v>
+      </c>
+      <c r="O655" t="s" s="2">
         <v>1397</v>
-      </c>
-      <c r="O655" t="s" s="2">
-        <v>1398</v>
       </c>
       <c r="P655" s="2"/>
       <c r="Q655" t="s" s="2">
@@ -77241,7 +77656,7 @@
         <v>75</v>
       </c>
       <c r="AG655" t="s" s="2">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="AH655" t="s" s="2">
         <v>76</v>
@@ -77261,10 +77676,10 @@
         <v>1123</v>
       </c>
       <c r="B656" t="s" s="2">
+        <v>1402</v>
+      </c>
+      <c r="C656" t="s" s="2">
         <v>1403</v>
-      </c>
-      <c r="C656" t="s" s="2">
-        <v>1404</v>
       </c>
       <c r="D656" s="2"/>
       <c r="E656" t="s" s="2">
@@ -77364,10 +77779,10 @@
         <v>1123</v>
       </c>
       <c r="B657" t="s" s="2">
+        <v>1404</v>
+      </c>
+      <c r="C657" t="s" s="2">
         <v>1405</v>
-      </c>
-      <c r="C657" t="s" s="2">
-        <v>1406</v>
       </c>
       <c r="D657" s="2"/>
       <c r="E657" t="s" s="2">
@@ -77469,10 +77884,10 @@
         <v>1123</v>
       </c>
       <c r="B658" t="s" s="2">
+        <v>1406</v>
+      </c>
+      <c r="C658" t="s" s="2">
         <v>1407</v>
-      </c>
-      <c r="C658" t="s" s="2">
-        <v>1408</v>
       </c>
       <c r="D658" s="2"/>
       <c r="E658" t="s" s="2">
@@ -77498,13 +77913,13 @@
         <v>83</v>
       </c>
       <c r="M658" t="s" s="2">
+        <v>1408</v>
+      </c>
+      <c r="N658" t="s" s="2">
         <v>1409</v>
       </c>
-      <c r="N658" t="s" s="2">
+      <c r="O658" t="s" s="2">
         <v>1410</v>
-      </c>
-      <c r="O658" t="s" s="2">
-        <v>1411</v>
       </c>
       <c r="P658" s="2"/>
       <c r="Q658" t="s" s="2">
@@ -77554,16 +77969,16 @@
         <v>75</v>
       </c>
       <c r="AG658" t="s" s="2">
+        <v>1411</v>
+      </c>
+      <c r="AH658" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI658" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ658" t="s" s="2">
         <v>1412</v>
-      </c>
-      <c r="AH658" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI658" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ658" t="s" s="2">
-        <v>1413</v>
       </c>
       <c r="AK658" t="s" s="2">
         <v>103</v>
@@ -77574,10 +77989,10 @@
         <v>1123</v>
       </c>
       <c r="B659" t="s" s="2">
+        <v>1413</v>
+      </c>
+      <c r="C659" t="s" s="2">
         <v>1414</v>
-      </c>
-      <c r="C659" t="s" s="2">
-        <v>1415</v>
       </c>
       <c r="D659" s="2"/>
       <c r="E659" t="s" s="2">
@@ -77603,13 +78018,13 @@
         <v>95</v>
       </c>
       <c r="M659" t="s" s="2">
+        <v>1415</v>
+      </c>
+      <c r="N659" t="s" s="2">
         <v>1416</v>
       </c>
-      <c r="N659" t="s" s="2">
+      <c r="O659" t="s" s="2">
         <v>1417</v>
-      </c>
-      <c r="O659" t="s" s="2">
-        <v>1418</v>
       </c>
       <c r="P659" s="2"/>
       <c r="Q659" t="s" s="2">
@@ -77638,28 +78053,28 @@
         <v>161</v>
       </c>
       <c r="Z659" t="s" s="2">
+        <v>1418</v>
+      </c>
+      <c r="AA659" t="s" s="2">
         <v>1419</v>
       </c>
-      <c r="AA659" t="s" s="2">
+      <c r="AB659" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC659" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD659" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE659" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF659" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG659" t="s" s="2">
         <v>1420</v>
-      </c>
-      <c r="AB659" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC659" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD659" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE659" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF659" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG659" t="s" s="2">
-        <v>1421</v>
       </c>
       <c r="AH659" t="s" s="2">
         <v>76</v>
@@ -77679,10 +78094,10 @@
         <v>1123</v>
       </c>
       <c r="B660" t="s" s="2">
+        <v>1421</v>
+      </c>
+      <c r="C660" t="s" s="2">
         <v>1422</v>
-      </c>
-      <c r="C660" t="s" s="2">
-        <v>1423</v>
       </c>
       <c r="D660" s="2"/>
       <c r="E660" t="s" s="2">
@@ -77714,7 +78129,7 @@
         <v>145</v>
       </c>
       <c r="O660" t="s" s="2">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="P660" s="2"/>
       <c r="Q660" t="s" s="2">
@@ -77764,7 +78179,7 @@
         <v>75</v>
       </c>
       <c r="AG660" t="s" s="2">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="AH660" t="s" s="2">
         <v>76</v>
@@ -77784,10 +78199,10 @@
         <v>1123</v>
       </c>
       <c r="B661" t="s" s="2">
+        <v>1425</v>
+      </c>
+      <c r="C661" t="s" s="2">
         <v>1426</v>
-      </c>
-      <c r="C661" t="s" s="2">
-        <v>1427</v>
       </c>
       <c r="D661" s="2"/>
       <c r="E661" t="s" s="2">
@@ -77813,13 +78228,13 @@
         <v>83</v>
       </c>
       <c r="M661" t="s" s="2">
+        <v>1427</v>
+      </c>
+      <c r="N661" t="s" s="2">
         <v>1428</v>
       </c>
-      <c r="N661" t="s" s="2">
+      <c r="O661" t="s" s="2">
         <v>1429</v>
-      </c>
-      <c r="O661" t="s" s="2">
-        <v>1430</v>
       </c>
       <c r="P661" s="2"/>
       <c r="Q661" t="s" s="2">
@@ -77869,7 +78284,7 @@
         <v>75</v>
       </c>
       <c r="AG661" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="AH661" t="s" s="2">
         <v>76</v>
@@ -77889,10 +78304,10 @@
         <v>1123</v>
       </c>
       <c r="B662" t="s" s="2">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="C662" t="s" s="2">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="D662" s="2"/>
       <c r="E662" t="s" s="2">
@@ -77918,16 +78333,16 @@
         <v>183</v>
       </c>
       <c r="M662" t="s" s="2">
+        <v>1432</v>
+      </c>
+      <c r="N662" t="s" s="2">
         <v>1433</v>
       </c>
-      <c r="N662" t="s" s="2">
+      <c r="O662" t="s" s="2">
         <v>1434</v>
       </c>
-      <c r="O662" t="s" s="2">
+      <c r="P662" t="s" s="2">
         <v>1435</v>
-      </c>
-      <c r="P662" t="s" s="2">
-        <v>1436</v>
       </c>
       <c r="Q662" t="s" s="2">
         <v>75</v>
@@ -77976,7 +78391,7 @@
         <v>75</v>
       </c>
       <c r="AG662" t="s" s="2">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="AH662" t="s" s="2">
         <v>76</v>
@@ -77996,10 +78411,10 @@
         <v>1123</v>
       </c>
       <c r="B663" t="s" s="2">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="C663" t="s" s="2">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="D663" s="2"/>
       <c r="E663" t="s" s="2">
@@ -78025,16 +78440,16 @@
         <v>549</v>
       </c>
       <c r="M663" t="s" s="2">
+        <v>1437</v>
+      </c>
+      <c r="N663" t="s" s="2">
         <v>1438</v>
       </c>
-      <c r="N663" t="s" s="2">
+      <c r="O663" t="s" s="2">
         <v>1439</v>
       </c>
-      <c r="O663" t="s" s="2">
+      <c r="P663" t="s" s="2">
         <v>1440</v>
-      </c>
-      <c r="P663" t="s" s="2">
-        <v>1441</v>
       </c>
       <c r="Q663" t="s" s="2">
         <v>75</v>
@@ -78083,7 +78498,7 @@
         <v>75</v>
       </c>
       <c r="AG663" t="s" s="2">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="AH663" t="s" s="2">
         <v>76</v>
@@ -78103,10 +78518,10 @@
         <v>1123</v>
       </c>
       <c r="B664" t="s" s="2">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="C664" t="s" s="2">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="D664" s="2"/>
       <c r="E664" t="s" s="2">
@@ -78206,10 +78621,10 @@
         <v>1123</v>
       </c>
       <c r="B665" t="s" s="2">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="C665" t="s" s="2">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="D665" s="2"/>
       <c r="E665" t="s" s="2">
@@ -78311,10 +78726,10 @@
         <v>1123</v>
       </c>
       <c r="B666" t="s" s="2">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="C666" t="s" s="2">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="D666" s="2"/>
       <c r="E666" t="s" s="2">
@@ -78418,10 +78833,10 @@
         <v>1123</v>
       </c>
       <c r="B667" t="s" s="2">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C667" t="s" s="2">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="D667" s="2"/>
       <c r="E667" t="s" s="2">
@@ -78444,16 +78859,16 @@
         <v>122</v>
       </c>
       <c r="L667" t="s" s="2">
+        <v>1445</v>
+      </c>
+      <c r="M667" t="s" s="2">
         <v>1446</v>
       </c>
-      <c r="M667" t="s" s="2">
+      <c r="N667" t="s" s="2">
         <v>1447</v>
       </c>
-      <c r="N667" t="s" s="2">
+      <c r="O667" t="s" s="2">
         <v>1448</v>
-      </c>
-      <c r="O667" t="s" s="2">
-        <v>1449</v>
       </c>
       <c r="P667" s="2"/>
       <c r="Q667" t="s" s="2">
@@ -78503,7 +78918,7 @@
         <v>75</v>
       </c>
       <c r="AG667" t="s" s="2">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="AH667" t="s" s="2">
         <v>82</v>
@@ -78523,10 +78938,10 @@
         <v>1123</v>
       </c>
       <c r="B668" t="s" s="2">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="C668" t="s" s="2">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="D668" s="2"/>
       <c r="E668" t="s" s="2">
@@ -78552,10 +78967,10 @@
         <v>149</v>
       </c>
       <c r="M668" t="s" s="2">
+        <v>1450</v>
+      </c>
+      <c r="N668" t="s" s="2">
         <v>1451</v>
-      </c>
-      <c r="N668" t="s" s="2">
-        <v>1452</v>
       </c>
       <c r="O668" s="2"/>
       <c r="P668" s="2"/>
@@ -78585,11 +79000,11 @@
         <v>128</v>
       </c>
       <c r="Z668" t="s" s="2">
+        <v>1451</v>
+      </c>
+      <c r="AA668" t="s" s="2">
         <v>1452</v>
       </c>
-      <c r="AA668" t="s" s="2">
-        <v>1453</v>
-      </c>
       <c r="AB668" t="s" s="2">
         <v>75</v>
       </c>
@@ -78606,7 +79021,7 @@
         <v>75</v>
       </c>
       <c r="AG668" t="s" s="2">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="AH668" t="s" s="2">
         <v>82</v>
@@ -78623,13 +79038,13 @@
     </row>
     <row r="669">
       <c r="A669" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B669" t="s" s="2">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="C669" t="s" s="2">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="D669" s="2"/>
       <c r="E669" t="s" s="2">
@@ -78655,10 +79070,10 @@
         <v>78</v>
       </c>
       <c r="M669" t="s" s="2">
+        <v>1460</v>
+      </c>
+      <c r="N669" t="s" s="2">
         <v>1461</v>
-      </c>
-      <c r="N669" t="s" s="2">
-        <v>1462</v>
       </c>
       <c r="O669" s="2"/>
       <c r="P669" s="2"/>
@@ -78709,7 +79124,7 @@
         <v>75</v>
       </c>
       <c r="AG669" t="s" s="2">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="AH669" t="s" s="2">
         <v>76</v>
@@ -78721,18 +79136,18 @@
         <v>75</v>
       </c>
       <c r="AK669" t="s" s="2">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B670" t="s" s="2">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="C670" t="s" s="2">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="D670" s="2"/>
       <c r="E670" t="s" s="2">
@@ -78831,13 +79246,13 @@
     </row>
     <row r="671">
       <c r="A671" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B671" t="s" s="2">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="C671" t="s" s="2">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="D671" s="2"/>
       <c r="E671" t="s" s="2">
@@ -78934,13 +79349,13 @@
     </row>
     <row r="672">
       <c r="A672" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B672" t="s" s="2">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="C672" t="s" s="2">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="D672" s="2"/>
       <c r="E672" t="s" s="2">
@@ -79039,13 +79454,13 @@
     </row>
     <row r="673">
       <c r="A673" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B673" t="s" s="2">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="C673" t="s" s="2">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="D673" s="2"/>
       <c r="E673" t="s" s="2">
@@ -79144,13 +79559,13 @@
     </row>
     <row r="674">
       <c r="A674" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B674" t="s" s="2">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="C674" t="s" s="2">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="D674" s="2"/>
       <c r="E674" t="s" s="2">
@@ -79249,13 +79664,13 @@
     </row>
     <row r="675">
       <c r="A675" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B675" t="s" s="2">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="C675" t="s" s="2">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="D675" s="2"/>
       <c r="E675" t="s" s="2">
@@ -79354,13 +79769,13 @@
     </row>
     <row r="676">
       <c r="A676" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B676" t="s" s="2">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="C676" t="s" s="2">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="D676" s="2"/>
       <c r="E676" t="s" s="2">
@@ -79459,13 +79874,13 @@
     </row>
     <row r="677">
       <c r="A677" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B677" t="s" s="2">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="C677" t="s" s="2">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="D677" s="2"/>
       <c r="E677" t="s" s="2">
@@ -79566,13 +79981,13 @@
     </row>
     <row r="678">
       <c r="A678" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B678" t="s" s="2">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="C678" t="s" s="2">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="D678" s="2"/>
       <c r="E678" t="s" s="2">
@@ -79598,14 +80013,14 @@
         <v>247</v>
       </c>
       <c r="M678" t="s" s="2">
+        <v>1472</v>
+      </c>
+      <c r="N678" t="s" s="2">
         <v>1473</v>
-      </c>
-      <c r="N678" t="s" s="2">
-        <v>1474</v>
       </c>
       <c r="O678" s="2"/>
       <c r="P678" t="s" s="2">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="Q678" t="s" s="2">
         <v>75</v>
@@ -79654,7 +80069,7 @@
         <v>75</v>
       </c>
       <c r="AG678" t="s" s="2">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="AH678" t="s" s="2">
         <v>76</v>
@@ -79671,13 +80086,13 @@
     </row>
     <row r="679">
       <c r="A679" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B679" t="s" s="2">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="C679" t="s" s="2">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="D679" s="2"/>
       <c r="E679" t="s" s="2">
@@ -79703,16 +80118,16 @@
         <v>327</v>
       </c>
       <c r="M679" t="s" s="2">
+        <v>1476</v>
+      </c>
+      <c r="N679" t="s" s="2">
         <v>1477</v>
       </c>
-      <c r="N679" t="s" s="2">
+      <c r="O679" t="s" s="2">
         <v>1478</v>
       </c>
-      <c r="O679" t="s" s="2">
+      <c r="P679" t="s" s="2">
         <v>1479</v>
-      </c>
-      <c r="P679" t="s" s="2">
-        <v>1480</v>
       </c>
       <c r="Q679" t="s" s="2">
         <v>75</v>
@@ -79763,7 +80178,7 @@
         <v>75</v>
       </c>
       <c r="AG679" t="s" s="2">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="AH679" t="s" s="2">
         <v>76</v>
@@ -79780,13 +80195,13 @@
     </row>
     <row r="680">
       <c r="A680" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B680" t="s" s="2">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="C680" t="s" s="2">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="D680" s="2"/>
       <c r="E680" t="s" s="2">
@@ -79812,16 +80227,16 @@
         <v>1106</v>
       </c>
       <c r="M680" t="s" s="2">
+        <v>1481</v>
+      </c>
+      <c r="N680" t="s" s="2">
         <v>1482</v>
       </c>
-      <c r="N680" t="s" s="2">
+      <c r="O680" t="s" s="2">
         <v>1483</v>
       </c>
-      <c r="O680" t="s" s="2">
+      <c r="P680" t="s" s="2">
         <v>1484</v>
-      </c>
-      <c r="P680" t="s" s="2">
-        <v>1485</v>
       </c>
       <c r="Q680" t="s" s="2">
         <v>75</v>
@@ -79870,7 +80285,7 @@
         <v>75</v>
       </c>
       <c r="AG680" t="s" s="2">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="AH680" t="s" s="2">
         <v>76</v>
@@ -79887,13 +80302,13 @@
     </row>
     <row r="681">
       <c r="A681" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B681" t="s" s="2">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="C681" t="s" s="2">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="D681" s="2"/>
       <c r="E681" t="s" s="2">
@@ -79919,16 +80334,16 @@
         <v>1072</v>
       </c>
       <c r="M681" t="s" s="2">
+        <v>1486</v>
+      </c>
+      <c r="N681" t="s" s="2">
         <v>1487</v>
       </c>
-      <c r="N681" t="s" s="2">
+      <c r="O681" t="s" s="2">
         <v>1488</v>
       </c>
-      <c r="O681" t="s" s="2">
+      <c r="P681" t="s" s="2">
         <v>1489</v>
-      </c>
-      <c r="P681" t="s" s="2">
-        <v>1490</v>
       </c>
       <c r="Q681" t="s" s="2">
         <v>75</v>
@@ -79977,7 +80392,7 @@
         <v>75</v>
       </c>
       <c r="AG681" t="s" s="2">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="AH681" t="s" s="2">
         <v>76</v>
@@ -79994,13 +80409,13 @@
     </row>
     <row r="682">
       <c r="A682" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B682" t="s" s="2">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="C682" t="s" s="2">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="D682" s="2"/>
       <c r="E682" t="s" s="2">
@@ -80026,16 +80441,16 @@
         <v>1080</v>
       </c>
       <c r="M682" t="s" s="2">
+        <v>1491</v>
+      </c>
+      <c r="N682" t="s" s="2">
         <v>1492</v>
       </c>
-      <c r="N682" t="s" s="2">
+      <c r="O682" t="s" s="2">
         <v>1493</v>
       </c>
-      <c r="O682" t="s" s="2">
+      <c r="P682" t="s" s="2">
         <v>1494</v>
-      </c>
-      <c r="P682" t="s" s="2">
-        <v>1495</v>
       </c>
       <c r="Q682" t="s" s="2">
         <v>75</v>
@@ -80084,7 +80499,7 @@
         <v>75</v>
       </c>
       <c r="AG682" t="s" s="2">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="AH682" t="s" s="2">
         <v>76</v>
@@ -80101,13 +80516,13 @@
     </row>
     <row r="683">
       <c r="A683" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B683" t="s" s="2">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="C683" t="s" s="2">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="D683" s="2"/>
       <c r="E683" t="s" s="2">
@@ -80136,11 +80551,11 @@
         <v>1226</v>
       </c>
       <c r="N683" t="s" s="2">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="O683" s="2"/>
       <c r="P683" t="s" s="2">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="Q683" t="s" s="2">
         <v>75</v>
@@ -80189,7 +80604,7 @@
         <v>75</v>
       </c>
       <c r="AG683" t="s" s="2">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="AH683" t="s" s="2">
         <v>76</v>
@@ -80206,13 +80621,13 @@
     </row>
     <row r="684">
       <c r="A684" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B684" t="s" s="2">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="C684" t="s" s="2">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="D684" s="2"/>
       <c r="E684" t="s" s="2">
@@ -80238,14 +80653,14 @@
         <v>1233</v>
       </c>
       <c r="M684" t="s" s="2">
+        <v>1498</v>
+      </c>
+      <c r="N684" t="s" s="2">
         <v>1499</v>
-      </c>
-      <c r="N684" t="s" s="2">
-        <v>1500</v>
       </c>
       <c r="O684" s="2"/>
       <c r="P684" t="s" s="2">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="Q684" t="s" s="2">
         <v>75</v>
@@ -80294,7 +80709,7 @@
         <v>75</v>
       </c>
       <c r="AG684" t="s" s="2">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="AH684" t="s" s="2">
         <v>76</v>
@@ -80311,13 +80726,13 @@
     </row>
     <row r="685">
       <c r="A685" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B685" t="s" s="2">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="C685" t="s" s="2">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="D685" s="2"/>
       <c r="E685" t="s" s="2">
@@ -80343,14 +80758,14 @@
         <v>1332</v>
       </c>
       <c r="M685" t="s" s="2">
+        <v>1502</v>
+      </c>
+      <c r="N685" t="s" s="2">
         <v>1503</v>
-      </c>
-      <c r="N685" t="s" s="2">
-        <v>1504</v>
       </c>
       <c r="O685" s="2"/>
       <c r="P685" t="s" s="2">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q685" t="s" s="2">
         <v>75</v>
@@ -80399,7 +80814,7 @@
         <v>75</v>
       </c>
       <c r="AG685" t="s" s="2">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="AH685" t="s" s="2">
         <v>76</v>
@@ -80416,13 +80831,13 @@
     </row>
     <row r="686">
       <c r="A686" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B686" t="s" s="2">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="C686" t="s" s="2">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D686" s="2"/>
       <c r="E686" t="s" s="2">
@@ -80448,10 +80863,10 @@
         <v>549</v>
       </c>
       <c r="M686" t="s" s="2">
+        <v>1506</v>
+      </c>
+      <c r="N686" t="s" s="2">
         <v>1507</v>
-      </c>
-      <c r="N686" t="s" s="2">
-        <v>1508</v>
       </c>
       <c r="O686" s="2"/>
       <c r="P686" s="2"/>
@@ -80490,10 +80905,10 @@
         <v>75</v>
       </c>
       <c r="AC686" t="s" s="2">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="AD686" t="s" s="2">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="AE686" t="s" s="2">
         <v>75</v>
@@ -80502,7 +80917,7 @@
         <v>92</v>
       </c>
       <c r="AG686" t="s" s="2">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="AH686" t="s" s="2">
         <v>76</v>
@@ -80519,13 +80934,13 @@
     </row>
     <row r="687">
       <c r="A687" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B687" t="s" s="2">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="C687" t="s" s="2">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="D687" s="2"/>
       <c r="E687" t="s" s="2">
@@ -80622,13 +81037,13 @@
     </row>
     <row r="688">
       <c r="A688" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B688" t="s" s="2">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="C688" t="s" s="2">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D688" s="2"/>
       <c r="E688" t="s" s="2">
@@ -80727,13 +81142,13 @@
     </row>
     <row r="689">
       <c r="A689" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B689" t="s" s="2">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="C689" t="s" s="2">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="D689" s="2"/>
       <c r="E689" t="s" s="2">
@@ -80834,13 +81249,13 @@
     </row>
     <row r="690">
       <c r="A690" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B690" t="s" s="2">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="C690" t="s" s="2">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="D690" s="2"/>
       <c r="E690" t="s" s="2">
@@ -80866,14 +81281,14 @@
         <v>247</v>
       </c>
       <c r="M690" t="s" s="2">
+        <v>1513</v>
+      </c>
+      <c r="N690" t="s" s="2">
         <v>1514</v>
-      </c>
-      <c r="N690" t="s" s="2">
-        <v>1515</v>
       </c>
       <c r="O690" s="2"/>
       <c r="P690" t="s" s="2">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="Q690" t="s" s="2">
         <v>75</v>
@@ -80922,7 +81337,7 @@
         <v>75</v>
       </c>
       <c r="AG690" t="s" s="2">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="AH690" t="s" s="2">
         <v>76</v>
@@ -80939,13 +81354,13 @@
     </row>
     <row r="691">
       <c r="A691" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B691" t="s" s="2">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C691" t="s" s="2">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D691" s="2"/>
       <c r="E691" t="s" s="2">
@@ -80971,10 +81386,10 @@
         <v>114</v>
       </c>
       <c r="M691" t="s" s="2">
+        <v>1517</v>
+      </c>
+      <c r="N691" t="s" s="2">
         <v>1518</v>
-      </c>
-      <c r="N691" t="s" s="2">
-        <v>1519</v>
       </c>
       <c r="O691" s="2"/>
       <c r="P691" s="2"/>
@@ -81004,11 +81419,11 @@
         <v>284</v>
       </c>
       <c r="Z691" t="s" s="2">
+        <v>1519</v>
+      </c>
+      <c r="AA691" t="s" s="2">
         <v>1520</v>
       </c>
-      <c r="AA691" t="s" s="2">
-        <v>1521</v>
-      </c>
       <c r="AB691" t="s" s="2">
         <v>75</v>
       </c>
@@ -81025,7 +81440,7 @@
         <v>75</v>
       </c>
       <c r="AG691" t="s" s="2">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="AH691" t="s" s="2">
         <v>82</v>
@@ -81042,13 +81457,13 @@
     </row>
     <row r="692">
       <c r="A692" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B692" t="s" s="2">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="C692" t="s" s="2">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="D692" s="2"/>
       <c r="E692" t="s" s="2">
@@ -81074,14 +81489,14 @@
         <v>179</v>
       </c>
       <c r="M692" t="s" s="2">
+        <v>1522</v>
+      </c>
+      <c r="N692" t="s" s="2">
         <v>1523</v>
-      </c>
-      <c r="N692" t="s" s="2">
-        <v>1524</v>
       </c>
       <c r="O692" s="2"/>
       <c r="P692" t="s" s="2">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="Q692" t="s" s="2">
         <v>75</v>
@@ -81130,7 +81545,7 @@
         <v>75</v>
       </c>
       <c r="AG692" t="s" s="2">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="AH692" t="s" s="2">
         <v>76</v>
@@ -81147,13 +81562,13 @@
     </row>
     <row r="693">
       <c r="A693" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B693" t="s" s="2">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="C693" t="s" s="2">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="D693" s="2"/>
       <c r="E693" t="s" s="2">
@@ -81179,10 +81594,10 @@
         <v>183</v>
       </c>
       <c r="M693" t="s" s="2">
+        <v>1526</v>
+      </c>
+      <c r="N693" t="s" s="2">
         <v>1527</v>
-      </c>
-      <c r="N693" t="s" s="2">
-        <v>1528</v>
       </c>
       <c r="O693" s="2"/>
       <c r="P693" s="2"/>
@@ -81233,7 +81648,7 @@
         <v>75</v>
       </c>
       <c r="AG693" t="s" s="2">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="AH693" t="s" s="2">
         <v>76</v>
@@ -81250,16 +81665,16 @@
     </row>
     <row r="694">
       <c r="A694" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B694" t="s" s="2">
+        <v>1528</v>
+      </c>
+      <c r="C694" t="s" s="2">
+        <v>1505</v>
+      </c>
+      <c r="D694" t="s" s="2">
         <v>1529</v>
-      </c>
-      <c r="C694" t="s" s="2">
-        <v>1506</v>
-      </c>
-      <c r="D694" t="s" s="2">
-        <v>1530</v>
       </c>
       <c r="E694" t="s" s="2">
         <v>75</v>
@@ -81284,10 +81699,10 @@
         <v>549</v>
       </c>
       <c r="M694" t="s" s="2">
+        <v>1506</v>
+      </c>
+      <c r="N694" t="s" s="2">
         <v>1507</v>
-      </c>
-      <c r="N694" t="s" s="2">
-        <v>1508</v>
       </c>
       <c r="O694" s="2"/>
       <c r="P694" s="2"/>
@@ -81338,7 +81753,7 @@
         <v>75</v>
       </c>
       <c r="AG694" t="s" s="2">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="AH694" t="s" s="2">
         <v>76</v>
@@ -81355,13 +81770,13 @@
     </row>
     <row r="695">
       <c r="A695" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B695" t="s" s="2">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="C695" t="s" s="2">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="D695" s="2"/>
       <c r="E695" t="s" s="2">
@@ -81458,13 +81873,13 @@
     </row>
     <row r="696">
       <c r="A696" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B696" t="s" s="2">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C696" t="s" s="2">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D696" s="2"/>
       <c r="E696" t="s" s="2">
@@ -81563,13 +81978,13 @@
     </row>
     <row r="697">
       <c r="A697" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B697" t="s" s="2">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C697" t="s" s="2">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="D697" s="2"/>
       <c r="E697" t="s" s="2">
@@ -81670,13 +82085,13 @@
     </row>
     <row r="698">
       <c r="A698" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B698" t="s" s="2">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C698" t="s" s="2">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="D698" s="2"/>
       <c r="E698" t="s" s="2">
@@ -81699,17 +82114,17 @@
         <v>75</v>
       </c>
       <c r="L698" t="s" s="2">
+        <v>1534</v>
+      </c>
+      <c r="M698" t="s" s="2">
         <v>1535</v>
-      </c>
-      <c r="M698" t="s" s="2">
-        <v>1536</v>
       </c>
       <c r="N698" t="s" s="2">
         <v>145</v>
       </c>
       <c r="O698" s="2"/>
       <c r="P698" t="s" s="2">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="Q698" t="s" s="2">
         <v>75</v>
@@ -81758,7 +82173,7 @@
         <v>75</v>
       </c>
       <c r="AG698" t="s" s="2">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="AH698" t="s" s="2">
         <v>76</v>
@@ -81775,13 +82190,13 @@
     </row>
     <row r="699">
       <c r="A699" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B699" t="s" s="2">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="C699" t="s" s="2">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D699" s="2"/>
       <c r="E699" t="s" s="2">
@@ -81807,10 +82222,10 @@
         <v>114</v>
       </c>
       <c r="M699" t="s" s="2">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="N699" t="s" s="2">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="O699" s="2"/>
       <c r="P699" s="2"/>
@@ -81841,7 +82256,7 @@
       </c>
       <c r="Z699" s="2"/>
       <c r="AA699" t="s" s="2">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="AB699" t="s" s="2">
         <v>75</v>
@@ -81859,7 +82274,7 @@
         <v>75</v>
       </c>
       <c r="AG699" t="s" s="2">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="AH699" t="s" s="2">
         <v>82</v>
@@ -81876,13 +82291,13 @@
     </row>
     <row r="700">
       <c r="A700" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B700" t="s" s="2">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="C700" t="s" s="2">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="D700" s="2"/>
       <c r="E700" t="s" s="2">
@@ -81908,14 +82323,14 @@
         <v>179</v>
       </c>
       <c r="M700" t="s" s="2">
+        <v>1522</v>
+      </c>
+      <c r="N700" t="s" s="2">
         <v>1523</v>
-      </c>
-      <c r="N700" t="s" s="2">
-        <v>1524</v>
       </c>
       <c r="O700" s="2"/>
       <c r="P700" t="s" s="2">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="Q700" t="s" s="2">
         <v>75</v>
@@ -81964,7 +82379,7 @@
         <v>75</v>
       </c>
       <c r="AG700" t="s" s="2">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="AH700" t="s" s="2">
         <v>76</v>
@@ -81981,13 +82396,13 @@
     </row>
     <row r="701">
       <c r="A701" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B701" t="s" s="2">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="C701" t="s" s="2">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="D701" s="2"/>
       <c r="E701" t="s" s="2">
@@ -82013,10 +82428,10 @@
         <v>183</v>
       </c>
       <c r="M701" t="s" s="2">
+        <v>1526</v>
+      </c>
+      <c r="N701" t="s" s="2">
         <v>1527</v>
-      </c>
-      <c r="N701" t="s" s="2">
-        <v>1528</v>
       </c>
       <c r="O701" s="2"/>
       <c r="P701" s="2"/>
@@ -82067,7 +82482,7 @@
         <v>75</v>
       </c>
       <c r="AG701" t="s" s="2">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="AH701" t="s" s="2">
         <v>76</v>
@@ -82084,13 +82499,13 @@
     </row>
     <row r="702">
       <c r="A702" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B702" t="s" s="2">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="C702" t="s" s="2">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="D702" s="2"/>
       <c r="E702" t="s" s="2">
@@ -82116,16 +82531,16 @@
         <v>114</v>
       </c>
       <c r="M702" t="s" s="2">
+        <v>1542</v>
+      </c>
+      <c r="N702" t="s" s="2">
         <v>1543</v>
       </c>
-      <c r="N702" t="s" s="2">
+      <c r="O702" t="s" s="2">
         <v>1544</v>
       </c>
-      <c r="O702" t="s" s="2">
+      <c r="P702" t="s" s="2">
         <v>1545</v>
-      </c>
-      <c r="P702" t="s" s="2">
-        <v>1546</v>
       </c>
       <c r="Q702" t="s" s="2">
         <v>75</v>
@@ -82174,7 +82589,7 @@
         <v>75</v>
       </c>
       <c r="AG702" t="s" s="2">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="AH702" t="s" s="2">
         <v>76</v>
@@ -82191,7 +82606,7 @@
     </row>
     <row r="703">
       <c r="A703" t="s" s="2">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B703" t="s" s="2">
         <v>142</v>
@@ -82294,7 +82709,7 @@
     </row>
     <row r="704">
       <c r="A704" t="s" s="2">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B704" t="s" s="2">
         <v>146</v>
@@ -82397,7 +82812,7 @@
     </row>
     <row r="705">
       <c r="A705" t="s" s="2">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B705" t="s" s="2">
         <v>147</v>
@@ -82502,7 +82917,7 @@
     </row>
     <row r="706">
       <c r="A706" t="s" s="2">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B706" t="s" s="2">
         <v>148</v>
@@ -82609,7 +83024,7 @@
     </row>
     <row r="707">
       <c r="A707" t="s" s="2">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B707" t="s" s="2">
         <v>156</v>
@@ -82716,7 +83131,7 @@
     </row>
     <row r="708">
       <c r="A708" t="s" s="2">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B708" t="s" s="2">
         <v>164</v>
@@ -82764,7 +83179,7 @@
       </c>
       <c r="R708" s="2"/>
       <c r="S708" t="s" s="2">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="T708" t="s" s="2">
         <v>75</v>
@@ -82823,7 +83238,7 @@
     </row>
     <row r="709">
       <c r="A709" t="s" s="2">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B709" t="s" s="2">
         <v>171</v>
@@ -82928,7 +83343,7 @@
     </row>
     <row r="710">
       <c r="A710" t="s" s="2">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B710" t="s" s="2">
         <v>178</v>
@@ -83031,7 +83446,7 @@
     </row>
     <row r="711">
       <c r="A711" t="s" s="2">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B711" t="s" s="2">
         <v>182</v>
@@ -83136,13 +83551,13 @@
     </row>
     <row r="712">
       <c r="A712" t="s" s="2">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B712" t="s" s="2">
-        <v>142</v>
+        <v>1557</v>
       </c>
       <c r="C712" t="s" s="2">
-        <v>142</v>
+        <v>1557</v>
       </c>
       <c r="D712" s="2"/>
       <c r="E712" t="s" s="2">
@@ -83168,10 +83583,10 @@
         <v>78</v>
       </c>
       <c r="M712" t="s" s="2">
-        <v>144</v>
+        <v>1559</v>
       </c>
       <c r="N712" t="s" s="2">
-        <v>145</v>
+        <v>1560</v>
       </c>
       <c r="O712" s="2"/>
       <c r="P712" s="2"/>
@@ -83222,7 +83637,7 @@
         <v>75</v>
       </c>
       <c r="AG712" t="s" s="2">
-        <v>142</v>
+        <v>1557</v>
       </c>
       <c r="AH712" t="s" s="2">
         <v>76</v>
@@ -83231,21 +83646,21 @@
         <v>77</v>
       </c>
       <c r="AJ712" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AK712" t="s" s="2">
-        <v>103</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="s" s="2">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B713" t="s" s="2">
-        <v>146</v>
+        <v>1561</v>
       </c>
       <c r="C713" t="s" s="2">
-        <v>146</v>
+        <v>1561</v>
       </c>
       <c r="D713" s="2"/>
       <c r="E713" t="s" s="2">
@@ -83265,18 +83680,20 @@
         <v>75</v>
       </c>
       <c r="K713" t="s" s="2">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="L713" t="s" s="2">
-        <v>83</v>
+        <v>201</v>
       </c>
       <c r="M713" t="s" s="2">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="N713" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="O713" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="O713" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P713" s="2"/>
       <c r="Q713" t="s" s="2">
         <v>75</v>
@@ -83325,7 +83742,7 @@
         <v>75</v>
       </c>
       <c r="AG713" t="s" s="2">
-        <v>86</v>
+        <v>205</v>
       </c>
       <c r="AH713" t="s" s="2">
         <v>76</v>
@@ -83342,24 +83759,24 @@
     </row>
     <row r="714">
       <c r="A714" t="s" s="2">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B714" t="s" s="2">
-        <v>147</v>
+        <v>1562</v>
       </c>
       <c r="C714" t="s" s="2">
-        <v>147</v>
+        <v>1562</v>
       </c>
       <c r="D714" s="2"/>
       <c r="E714" t="s" s="2">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="F714" s="2"/>
       <c r="G714" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H714" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="I714" t="s" s="2">
         <v>75</v>
@@ -83368,20 +83785,18 @@
         <v>75</v>
       </c>
       <c r="K714" t="s" s="2">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="L714" t="s" s="2">
-        <v>88</v>
+        <v>207</v>
       </c>
       <c r="M714" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="N714" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O714" t="s" s="2">
-        <v>120</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="O714" s="2"/>
       <c r="P714" s="2"/>
       <c r="Q714" t="s" s="2">
         <v>75</v>
@@ -83418,42 +83833,42 @@
         <v>75</v>
       </c>
       <c r="AC714" t="s" s="2">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AD714" t="s" s="2">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="AE714" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF714" t="s" s="2">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="AG714" t="s" s="2">
-        <v>93</v>
+        <v>210</v>
       </c>
       <c r="AH714" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI714" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AJ714" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK714" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="s" s="2">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B715" t="s" s="2">
-        <v>148</v>
+        <v>1563</v>
       </c>
       <c r="C715" t="s" s="2">
-        <v>148</v>
+        <v>1563</v>
       </c>
       <c r="D715" s="2"/>
       <c r="E715" t="s" s="2">
@@ -83476,26 +83891,24 @@
         <v>122</v>
       </c>
       <c r="L715" t="s" s="2">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="M715" t="s" s="2">
-        <v>150</v>
+        <v>212</v>
       </c>
       <c r="N715" t="s" s="2">
-        <v>151</v>
+        <v>213</v>
       </c>
       <c r="O715" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="P715" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="P715" s="2"/>
       <c r="Q715" t="s" s="2">
         <v>75</v>
       </c>
       <c r="R715" s="2"/>
       <c r="S715" t="s" s="2">
-        <v>918</v>
+        <v>75</v>
       </c>
       <c r="T715" t="s" s="2">
         <v>75</v>
@@ -83513,13 +83926,13 @@
         <v>75</v>
       </c>
       <c r="Y715" t="s" s="2">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="Z715" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AA715" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AB715" t="s" s="2">
         <v>75</v>
@@ -83537,7 +83950,7 @@
         <v>75</v>
       </c>
       <c r="AG715" t="s" s="2">
-        <v>148</v>
+        <v>215</v>
       </c>
       <c r="AH715" t="s" s="2">
         <v>76</v>
@@ -83554,13 +83967,13 @@
     </row>
     <row r="716">
       <c r="A716" t="s" s="2">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B716" t="s" s="2">
-        <v>156</v>
+        <v>1564</v>
       </c>
       <c r="C716" t="s" s="2">
-        <v>156</v>
+        <v>1564</v>
       </c>
       <c r="D716" s="2"/>
       <c r="E716" t="s" s="2">
@@ -83580,23 +83993,21 @@
         <v>75</v>
       </c>
       <c r="K716" t="s" s="2">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="L716" t="s" s="2">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="M716" t="s" s="2">
-        <v>157</v>
+        <v>217</v>
       </c>
       <c r="N716" t="s" s="2">
-        <v>158</v>
+        <v>218</v>
       </c>
       <c r="O716" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="P716" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="P716" s="2"/>
       <c r="Q716" t="s" s="2">
         <v>75</v>
       </c>
@@ -83620,13 +84031,13 @@
         <v>75</v>
       </c>
       <c r="Y716" t="s" s="2">
-        <v>161</v>
+        <v>220</v>
       </c>
       <c r="Z716" t="s" s="2">
-        <v>162</v>
+        <v>221</v>
       </c>
       <c r="AA716" t="s" s="2">
-        <v>163</v>
+        <v>222</v>
       </c>
       <c r="AB716" t="s" s="2">
         <v>75</v>
@@ -83644,7 +84055,7 @@
         <v>75</v>
       </c>
       <c r="AG716" t="s" s="2">
-        <v>156</v>
+        <v>223</v>
       </c>
       <c r="AH716" t="s" s="2">
         <v>76</v>
@@ -83661,21 +84072,21 @@
     </row>
     <row r="717">
       <c r="A717" t="s" s="2">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B717" t="s" s="2">
-        <v>164</v>
+        <v>1565</v>
       </c>
       <c r="C717" t="s" s="2">
-        <v>164</v>
+        <v>1565</v>
       </c>
       <c r="D717" s="2"/>
       <c r="E717" t="s" s="2">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="F717" s="2"/>
       <c r="G717" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H717" t="s" s="2">
         <v>82</v>
@@ -83687,35 +84098,33 @@
         <v>75</v>
       </c>
       <c r="K717" t="s" s="2">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="L717" t="s" s="2">
-        <v>95</v>
+        <v>226</v>
       </c>
       <c r="M717" t="s" s="2">
-        <v>165</v>
+        <v>227</v>
       </c>
       <c r="N717" t="s" s="2">
-        <v>166</v>
+        <v>228</v>
       </c>
       <c r="O717" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="P717" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="P717" s="2"/>
       <c r="Q717" t="s" s="2">
         <v>75</v>
       </c>
       <c r="R717" s="2"/>
       <c r="S717" t="s" s="2">
-        <v>1558</v>
+        <v>75</v>
       </c>
       <c r="T717" t="s" s="2">
         <v>75</v>
       </c>
       <c r="U717" t="s" s="2">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="V717" t="s" s="2">
         <v>75</v>
@@ -83751,7 +84160,7 @@
         <v>75</v>
       </c>
       <c r="AG717" t="s" s="2">
-        <v>164</v>
+        <v>230</v>
       </c>
       <c r="AH717" t="s" s="2">
         <v>76</v>
@@ -83768,24 +84177,24 @@
     </row>
     <row r="718">
       <c r="A718" t="s" s="2">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B718" t="s" s="2">
-        <v>171</v>
+        <v>1566</v>
       </c>
       <c r="C718" t="s" s="2">
-        <v>171</v>
+        <v>1566</v>
       </c>
       <c r="D718" s="2"/>
       <c r="E718" t="s" s="2">
-        <v>75</v>
+        <v>232</v>
       </c>
       <c r="F718" s="2"/>
       <c r="G718" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H718" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I718" t="s" s="2">
         <v>75</v>
@@ -83794,19 +84203,19 @@
         <v>75</v>
       </c>
       <c r="K718" t="s" s="2">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="L718" t="s" s="2">
-        <v>83</v>
+        <v>233</v>
       </c>
       <c r="M718" t="s" s="2">
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="N718" t="s" s="2">
-        <v>173</v>
+        <v>235</v>
       </c>
       <c r="O718" t="s" s="2">
-        <v>174</v>
+        <v>236</v>
       </c>
       <c r="P718" s="2"/>
       <c r="Q718" t="s" s="2">
@@ -83820,7 +84229,7 @@
         <v>75</v>
       </c>
       <c r="U718" t="s" s="2">
-        <v>175</v>
+        <v>75</v>
       </c>
       <c r="V718" t="s" s="2">
         <v>75</v>
@@ -83856,41 +84265,41 @@
         <v>75</v>
       </c>
       <c r="AG718" t="s" s="2">
-        <v>171</v>
+        <v>237</v>
       </c>
       <c r="AH718" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI718" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AJ718" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK718" t="s" s="2">
-        <v>1559</v>
+        <v>75</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="s" s="2">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B719" t="s" s="2">
-        <v>178</v>
+        <v>1567</v>
       </c>
       <c r="C719" t="s" s="2">
-        <v>178</v>
+        <v>1567</v>
       </c>
       <c r="D719" s="2"/>
       <c r="E719" t="s" s="2">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="F719" s="2"/>
       <c r="G719" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H719" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I719" t="s" s="2">
         <v>75</v>
@@ -83899,18 +84308,20 @@
         <v>75</v>
       </c>
       <c r="K719" t="s" s="2">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="L719" t="s" s="2">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="M719" t="s" s="2">
-        <v>180</v>
+        <v>118</v>
       </c>
       <c r="N719" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O719" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O719" t="s" s="2">
+        <v>120</v>
+      </c>
       <c r="P719" s="2"/>
       <c r="Q719" t="s" s="2">
         <v>75</v>
@@ -83959,64 +84370,66 @@
         <v>75</v>
       </c>
       <c r="AG719" t="s" s="2">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="AH719" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI719" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AJ719" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK719" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="s" s="2">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B720" t="s" s="2">
-        <v>182</v>
+        <v>1568</v>
       </c>
       <c r="C720" t="s" s="2">
-        <v>182</v>
+        <v>1568</v>
       </c>
       <c r="D720" s="2"/>
       <c r="E720" t="s" s="2">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="F720" s="2"/>
       <c r="G720" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H720" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I720" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J720" t="s" s="2">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="K720" t="s" s="2">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="L720" t="s" s="2">
-        <v>183</v>
+        <v>88</v>
       </c>
       <c r="M720" t="s" s="2">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="N720" t="s" s="2">
-        <v>185</v>
+        <v>243</v>
       </c>
       <c r="O720" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="P720" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="P720" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="Q720" t="s" s="2">
         <v>75</v>
       </c>
@@ -84064,30 +84477,30 @@
         <v>75</v>
       </c>
       <c r="AG720" t="s" s="2">
-        <v>182</v>
+        <v>245</v>
       </c>
       <c r="AH720" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI720" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AJ720" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK720" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="s" s="2">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="B721" t="s" s="2">
-        <v>142</v>
+        <v>1569</v>
       </c>
       <c r="C721" t="s" s="2">
-        <v>142</v>
+        <v>1569</v>
       </c>
       <c r="D721" s="2"/>
       <c r="E721" t="s" s="2">
@@ -84107,19 +84520,21 @@
         <v>75</v>
       </c>
       <c r="K721" t="s" s="2">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="L721" t="s" s="2">
-        <v>78</v>
+        <v>247</v>
       </c>
       <c r="M721" t="s" s="2">
-        <v>144</v>
+        <v>1570</v>
       </c>
       <c r="N721" t="s" s="2">
-        <v>145</v>
+        <v>1571</v>
       </c>
       <c r="O721" s="2"/>
-      <c r="P721" s="2"/>
+      <c r="P721" t="s" s="2">
+        <v>1572</v>
+      </c>
       <c r="Q721" t="s" s="2">
         <v>75</v>
       </c>
@@ -84155,19 +84570,17 @@
         <v>75</v>
       </c>
       <c r="AC721" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD721" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="AD721" s="2"/>
       <c r="AE721" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF721" t="s" s="2">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="AG721" t="s" s="2">
-        <v>142</v>
+        <v>1569</v>
       </c>
       <c r="AH721" t="s" s="2">
         <v>76</v>
@@ -84176,7 +84589,7 @@
         <v>77</v>
       </c>
       <c r="AJ721" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AK721" t="s" s="2">
         <v>103</v>
@@ -84184,15 +84597,17 @@
     </row>
     <row r="722">
       <c r="A722" t="s" s="2">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="B722" t="s" s="2">
-        <v>146</v>
+        <v>1573</v>
       </c>
       <c r="C722" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="D722" s="2"/>
+        <v>1569</v>
+      </c>
+      <c r="D722" t="s" s="2">
+        <v>1147</v>
+      </c>
       <c r="E722" t="s" s="2">
         <v>75</v>
       </c>
@@ -84213,16 +84628,18 @@
         <v>75</v>
       </c>
       <c r="L722" t="s" s="2">
-        <v>83</v>
+        <v>1148</v>
       </c>
       <c r="M722" t="s" s="2">
-        <v>84</v>
+        <v>1149</v>
       </c>
       <c r="N722" t="s" s="2">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="O722" s="2"/>
-      <c r="P722" s="2"/>
+      <c r="P722" t="s" s="2">
+        <v>1572</v>
+      </c>
       <c r="Q722" t="s" s="2">
         <v>75</v>
       </c>
@@ -84270,41 +84687,43 @@
         <v>75</v>
       </c>
       <c r="AG722" t="s" s="2">
-        <v>86</v>
+        <v>1569</v>
       </c>
       <c r="AH722" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI722" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AJ722" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AK722" t="s" s="2">
-        <v>75</v>
+        <v>103</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="s" s="2">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="B723" t="s" s="2">
-        <v>147</v>
+        <v>1574</v>
       </c>
       <c r="C723" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="D723" s="2"/>
+        <v>1569</v>
+      </c>
+      <c r="D723" t="s" s="2">
+        <v>1151</v>
+      </c>
       <c r="E723" t="s" s="2">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="F723" s="2"/>
       <c r="G723" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H723" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="I723" t="s" s="2">
         <v>75</v>
@@ -84316,18 +84735,18 @@
         <v>75</v>
       </c>
       <c r="L723" t="s" s="2">
-        <v>88</v>
+        <v>1152</v>
       </c>
       <c r="M723" t="s" s="2">
-        <v>118</v>
+        <v>1153</v>
       </c>
       <c r="N723" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O723" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="P723" s="2"/>
+        <v>145</v>
+      </c>
+      <c r="O723" s="2"/>
+      <c r="P723" t="s" s="2">
+        <v>1572</v>
+      </c>
       <c r="Q723" t="s" s="2">
         <v>75</v>
       </c>
@@ -84363,19 +84782,19 @@
         <v>75</v>
       </c>
       <c r="AC723" t="s" s="2">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AD723" t="s" s="2">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="AE723" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF723" t="s" s="2">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="AG723" t="s" s="2">
-        <v>93</v>
+        <v>1569</v>
       </c>
       <c r="AH723" t="s" s="2">
         <v>76</v>
@@ -84384,23 +84803,25 @@
         <v>77</v>
       </c>
       <c r="AJ723" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AK723" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="s" s="2">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="B724" t="s" s="2">
-        <v>148</v>
+        <v>1575</v>
       </c>
       <c r="C724" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="D724" s="2"/>
+        <v>1569</v>
+      </c>
+      <c r="D724" t="s" s="2">
+        <v>1155</v>
+      </c>
       <c r="E724" t="s" s="2">
         <v>75</v>
       </c>
@@ -84415,32 +84836,30 @@
         <v>75</v>
       </c>
       <c r="J724" t="s" s="2">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="K724" t="s" s="2">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="L724" t="s" s="2">
-        <v>149</v>
+        <v>1156</v>
       </c>
       <c r="M724" t="s" s="2">
-        <v>150</v>
+        <v>1157</v>
       </c>
       <c r="N724" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O724" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="O724" s="2"/>
       <c r="P724" t="s" s="2">
-        <v>153</v>
+        <v>1572</v>
       </c>
       <c r="Q724" t="s" s="2">
         <v>75</v>
       </c>
       <c r="R724" s="2"/>
       <c r="S724" t="s" s="2">
-        <v>934</v>
+        <v>75</v>
       </c>
       <c r="T724" t="s" s="2">
         <v>75</v>
@@ -84458,13 +84877,13 @@
         <v>75</v>
       </c>
       <c r="Y724" t="s" s="2">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="Z724" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AA724" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AB724" t="s" s="2">
         <v>75</v>
@@ -84482,16 +84901,16 @@
         <v>75</v>
       </c>
       <c r="AG724" t="s" s="2">
-        <v>148</v>
+        <v>1569</v>
       </c>
       <c r="AH724" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI724" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AJ724" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AK724" t="s" s="2">
         <v>103</v>
@@ -84499,13 +84918,13 @@
     </row>
     <row r="725">
       <c r="A725" t="s" s="2">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="B725" t="s" s="2">
-        <v>156</v>
+        <v>1576</v>
       </c>
       <c r="C725" t="s" s="2">
-        <v>156</v>
+        <v>1576</v>
       </c>
       <c r="D725" s="2"/>
       <c r="E725" t="s" s="2">
@@ -84522,30 +84941,32 @@
         <v>75</v>
       </c>
       <c r="J725" t="s" s="2">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="K725" t="s" s="2">
         <v>122</v>
       </c>
       <c r="L725" t="s" s="2">
-        <v>114</v>
+        <v>327</v>
       </c>
       <c r="M725" t="s" s="2">
-        <v>157</v>
+        <v>1577</v>
       </c>
       <c r="N725" t="s" s="2">
-        <v>158</v>
+        <v>1578</v>
       </c>
       <c r="O725" t="s" s="2">
-        <v>159</v>
+        <v>1579</v>
       </c>
       <c r="P725" t="s" s="2">
-        <v>160</v>
+        <v>1580</v>
       </c>
       <c r="Q725" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="R725" s="2"/>
+      <c r="R725" t="s" s="2">
+        <v>1054</v>
+      </c>
       <c r="S725" t="s" s="2">
         <v>75</v>
       </c>
@@ -84565,13 +84986,13 @@
         <v>75</v>
       </c>
       <c r="Y725" t="s" s="2">
-        <v>161</v>
+        <v>75</v>
       </c>
       <c r="Z725" t="s" s="2">
-        <v>162</v>
+        <v>75</v>
       </c>
       <c r="AA725" t="s" s="2">
-        <v>163</v>
+        <v>75</v>
       </c>
       <c r="AB725" t="s" s="2">
         <v>75</v>
@@ -84589,7 +85010,7 @@
         <v>75</v>
       </c>
       <c r="AG725" t="s" s="2">
-        <v>156</v>
+        <v>1576</v>
       </c>
       <c r="AH725" t="s" s="2">
         <v>76</v>
@@ -84606,13 +85027,13 @@
     </row>
     <row r="726">
       <c r="A726" t="s" s="2">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="B726" t="s" s="2">
-        <v>164</v>
+        <v>1581</v>
       </c>
       <c r="C726" t="s" s="2">
-        <v>164</v>
+        <v>1581</v>
       </c>
       <c r="D726" s="2"/>
       <c r="E726" t="s" s="2">
@@ -84635,32 +85056,30 @@
         <v>122</v>
       </c>
       <c r="L726" t="s" s="2">
-        <v>95</v>
+        <v>842</v>
       </c>
       <c r="M726" t="s" s="2">
-        <v>165</v>
+        <v>1582</v>
       </c>
       <c r="N726" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="O726" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>1583</v>
+      </c>
+      <c r="O726" s="2"/>
       <c r="P726" t="s" s="2">
-        <v>168</v>
+        <v>1584</v>
       </c>
       <c r="Q726" t="s" s="2">
         <v>75</v>
       </c>
       <c r="R726" s="2"/>
       <c r="S726" t="s" s="2">
-        <v>1565</v>
+        <v>75</v>
       </c>
       <c r="T726" t="s" s="2">
         <v>75</v>
       </c>
       <c r="U726" t="s" s="2">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="V726" t="s" s="2">
         <v>75</v>
@@ -84696,10 +85115,10 @@
         <v>75</v>
       </c>
       <c r="AG726" t="s" s="2">
-        <v>164</v>
+        <v>1581</v>
       </c>
       <c r="AH726" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI726" t="s" s="2">
         <v>82</v>
@@ -84713,13 +85132,13 @@
     </row>
     <row r="727">
       <c r="A727" t="s" s="2">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="B727" t="s" s="2">
-        <v>171</v>
+        <v>1585</v>
       </c>
       <c r="C727" t="s" s="2">
-        <v>171</v>
+        <v>1585</v>
       </c>
       <c r="D727" s="2"/>
       <c r="E727" t="s" s="2">
@@ -84727,10 +85146,10 @@
       </c>
       <c r="F727" s="2"/>
       <c r="G727" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H727" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I727" t="s" s="2">
         <v>75</v>
@@ -84742,18 +85161,18 @@
         <v>122</v>
       </c>
       <c r="L727" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="M727" t="s" s="2">
-        <v>172</v>
+        <v>1586</v>
       </c>
       <c r="N727" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="O727" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="P727" s="2"/>
+        <v>1587</v>
+      </c>
+      <c r="O727" s="2"/>
+      <c r="P727" t="s" s="2">
+        <v>1588</v>
+      </c>
       <c r="Q727" t="s" s="2">
         <v>75</v>
       </c>
@@ -84765,7 +85184,7 @@
         <v>75</v>
       </c>
       <c r="U727" t="s" s="2">
-        <v>175</v>
+        <v>75</v>
       </c>
       <c r="V727" t="s" s="2">
         <v>75</v>
@@ -84774,16 +85193,14 @@
         <v>75</v>
       </c>
       <c r="X727" t="s" s="2">
-        <v>920</v>
+        <v>75</v>
       </c>
       <c r="Y727" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z727" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="Z727" s="2"/>
       <c r="AA727" t="s" s="2">
-        <v>75</v>
+        <v>1350</v>
       </c>
       <c r="AB727" t="s" s="2">
         <v>75</v>
@@ -84801,30 +85218,30 @@
         <v>75</v>
       </c>
       <c r="AG727" t="s" s="2">
-        <v>171</v>
+        <v>1585</v>
       </c>
       <c r="AH727" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI727" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AJ727" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK727" t="s" s="2">
-        <v>1566</v>
+        <v>103</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="s" s="2">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="B728" t="s" s="2">
-        <v>178</v>
+        <v>1589</v>
       </c>
       <c r="C728" t="s" s="2">
-        <v>178</v>
+        <v>1589</v>
       </c>
       <c r="D728" s="2"/>
       <c r="E728" t="s" s="2">
@@ -84835,7 +85252,7 @@
         <v>76</v>
       </c>
       <c r="H728" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I728" t="s" s="2">
         <v>75</v>
@@ -84847,16 +85264,18 @@
         <v>122</v>
       </c>
       <c r="L728" t="s" s="2">
-        <v>179</v>
+        <v>1106</v>
       </c>
       <c r="M728" t="s" s="2">
-        <v>180</v>
+        <v>1590</v>
       </c>
       <c r="N728" t="s" s="2">
-        <v>181</v>
+        <v>1591</v>
       </c>
       <c r="O728" s="2"/>
-      <c r="P728" s="2"/>
+      <c r="P728" t="s" s="2">
+        <v>1592</v>
+      </c>
       <c r="Q728" t="s" s="2">
         <v>75</v>
       </c>
@@ -84892,25 +85311,23 @@
         <v>75</v>
       </c>
       <c r="AC728" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD728" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>1168</v>
+      </c>
+      <c r="AD728" s="2"/>
       <c r="AE728" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF728" t="s" s="2">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="AG728" t="s" s="2">
-        <v>178</v>
+        <v>1589</v>
       </c>
       <c r="AH728" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI728" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AJ728" t="s" s="2">
         <v>75</v>
@@ -84921,15 +85338,17 @@
     </row>
     <row r="729">
       <c r="A729" t="s" s="2">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="B729" t="s" s="2">
-        <v>182</v>
+        <v>1593</v>
       </c>
       <c r="C729" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="D729" s="2"/>
+        <v>1589</v>
+      </c>
+      <c r="D729" t="s" s="2">
+        <v>918</v>
+      </c>
       <c r="E729" t="s" s="2">
         <v>75</v>
       </c>
@@ -84950,18 +85369,18 @@
         <v>122</v>
       </c>
       <c r="L729" t="s" s="2">
-        <v>183</v>
+        <v>1106</v>
       </c>
       <c r="M729" t="s" s="2">
-        <v>184</v>
+        <v>1170</v>
       </c>
       <c r="N729" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="O729" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="P729" s="2"/>
+        <v>1591</v>
+      </c>
+      <c r="O729" s="2"/>
+      <c r="P729" t="s" s="2">
+        <v>1592</v>
+      </c>
       <c r="Q729" t="s" s="2">
         <v>75</v>
       </c>
@@ -85009,18 +85428,4115 @@
         <v>75</v>
       </c>
       <c r="AG729" t="s" s="2">
+        <v>1589</v>
+      </c>
+      <c r="AH729" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI729" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ729" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK729" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="B730" t="s" s="2">
+        <v>1594</v>
+      </c>
+      <c r="C730" t="s" s="2">
+        <v>1595</v>
+      </c>
+      <c r="D730" s="2"/>
+      <c r="E730" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F730" s="2"/>
+      <c r="G730" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H730" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I730" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J730" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K730" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L730" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M730" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="N730" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="O730" s="2"/>
+      <c r="P730" s="2"/>
+      <c r="Q730" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R730" s="2"/>
+      <c r="S730" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T730" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U730" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V730" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W730" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X730" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y730" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z730" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA730" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB730" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC730" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD730" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE730" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF730" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG730" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH730" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI730" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ730" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK730" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="B731" t="s" s="2">
+        <v>1596</v>
+      </c>
+      <c r="C731" t="s" s="2">
+        <v>1597</v>
+      </c>
+      <c r="D731" s="2"/>
+      <c r="E731" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F731" s="2"/>
+      <c r="G731" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H731" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I731" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J731" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K731" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L731" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="M731" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N731" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="O731" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="P731" s="2"/>
+      <c r="Q731" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R731" s="2"/>
+      <c r="S731" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T731" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U731" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V731" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W731" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X731" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y731" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z731" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA731" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB731" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC731" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AD731" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AE731" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF731" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AG731" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH731" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI731" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ731" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK731" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="B732" t="s" s="2">
+        <v>1598</v>
+      </c>
+      <c r="C732" t="s" s="2">
+        <v>1599</v>
+      </c>
+      <c r="D732" s="2"/>
+      <c r="E732" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F732" s="2"/>
+      <c r="G732" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H732" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I732" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J732" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="K732" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L732" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="M732" t="s" s="2">
+        <v>1177</v>
+      </c>
+      <c r="N732" t="s" s="2">
+        <v>1178</v>
+      </c>
+      <c r="O732" t="s" s="2">
+        <v>1179</v>
+      </c>
+      <c r="P732" t="s" s="2">
+        <v>1180</v>
+      </c>
+      <c r="Q732" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R732" s="2"/>
+      <c r="S732" t="s" s="2">
+        <v>918</v>
+      </c>
+      <c r="T732" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U732" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V732" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W732" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X732" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y732" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="Z732" t="s" s="2">
+        <v>1181</v>
+      </c>
+      <c r="AA732" t="s" s="2">
+        <v>1182</v>
+      </c>
+      <c r="AB732" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC732" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD732" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE732" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF732" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG732" t="s" s="2">
+        <v>1183</v>
+      </c>
+      <c r="AH732" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI732" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ732" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK732" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="B733" t="s" s="2">
+        <v>1600</v>
+      </c>
+      <c r="C733" t="s" s="2">
+        <v>1601</v>
+      </c>
+      <c r="D733" s="2"/>
+      <c r="E733" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F733" s="2"/>
+      <c r="G733" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H733" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I733" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J733" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K733" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L733" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M733" t="s" s="2">
+        <v>1186</v>
+      </c>
+      <c r="N733" t="s" s="2">
+        <v>1187</v>
+      </c>
+      <c r="O733" t="s" s="2">
+        <v>1188</v>
+      </c>
+      <c r="P733" t="s" s="2">
+        <v>1189</v>
+      </c>
+      <c r="Q733" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R733" s="2"/>
+      <c r="S733" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T733" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U733" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V733" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W733" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X733" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y733" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z733" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA733" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB733" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC733" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD733" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE733" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF733" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG733" t="s" s="2">
+        <v>1190</v>
+      </c>
+      <c r="AH733" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI733" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ733" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK733" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="B734" t="s" s="2">
+        <v>1602</v>
+      </c>
+      <c r="C734" t="s" s="2">
+        <v>1603</v>
+      </c>
+      <c r="D734" s="2"/>
+      <c r="E734" t="s" s="2">
+        <v>1193</v>
+      </c>
+      <c r="F734" s="2"/>
+      <c r="G734" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H734" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I734" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J734" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K734" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L734" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M734" t="s" s="2">
+        <v>1194</v>
+      </c>
+      <c r="N734" t="s" s="2">
+        <v>1195</v>
+      </c>
+      <c r="O734" t="s" s="2">
+        <v>1196</v>
+      </c>
+      <c r="P734" s="2"/>
+      <c r="Q734" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R734" s="2"/>
+      <c r="S734" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T734" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U734" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V734" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W734" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X734" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y734" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z734" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA734" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB734" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC734" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD734" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE734" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF734" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG734" t="s" s="2">
+        <v>1197</v>
+      </c>
+      <c r="AH734" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI734" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ734" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK734" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="B735" t="s" s="2">
+        <v>1604</v>
+      </c>
+      <c r="C735" t="s" s="2">
+        <v>1605</v>
+      </c>
+      <c r="D735" s="2"/>
+      <c r="E735" t="s" s="2">
+        <v>1200</v>
+      </c>
+      <c r="F735" s="2"/>
+      <c r="G735" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H735" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I735" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J735" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K735" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L735" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M735" t="s" s="2">
+        <v>1201</v>
+      </c>
+      <c r="N735" t="s" s="2">
+        <v>1202</v>
+      </c>
+      <c r="O735" t="s" s="2">
+        <v>1203</v>
+      </c>
+      <c r="P735" s="2"/>
+      <c r="Q735" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R735" s="2"/>
+      <c r="S735" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T735" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U735" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V735" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W735" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X735" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y735" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z735" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA735" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB735" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC735" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD735" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE735" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF735" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG735" t="s" s="2">
+        <v>1204</v>
+      </c>
+      <c r="AH735" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI735" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ735" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK735" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="B736" t="s" s="2">
+        <v>1606</v>
+      </c>
+      <c r="C736" t="s" s="2">
+        <v>1607</v>
+      </c>
+      <c r="D736" s="2"/>
+      <c r="E736" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F736" s="2"/>
+      <c r="G736" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H736" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I736" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J736" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K736" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L736" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M736" t="s" s="2">
+        <v>1207</v>
+      </c>
+      <c r="N736" t="s" s="2">
+        <v>1208</v>
+      </c>
+      <c r="O736" s="2"/>
+      <c r="P736" s="2"/>
+      <c r="Q736" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R736" s="2"/>
+      <c r="S736" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T736" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U736" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V736" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W736" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X736" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y736" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z736" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA736" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB736" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC736" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD736" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE736" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF736" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG736" t="s" s="2">
+        <v>1209</v>
+      </c>
+      <c r="AH736" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI736" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ736" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK736" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="B737" t="s" s="2">
+        <v>1608</v>
+      </c>
+      <c r="C737" t="s" s="2">
+        <v>1609</v>
+      </c>
+      <c r="D737" s="2"/>
+      <c r="E737" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F737" s="2"/>
+      <c r="G737" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H737" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I737" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J737" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K737" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L737" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M737" t="s" s="2">
+        <v>1212</v>
+      </c>
+      <c r="N737" t="s" s="2">
+        <v>1213</v>
+      </c>
+      <c r="O737" s="2"/>
+      <c r="P737" s="2"/>
+      <c r="Q737" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R737" s="2"/>
+      <c r="S737" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T737" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U737" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V737" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W737" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X737" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y737" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z737" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA737" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB737" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC737" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD737" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE737" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF737" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG737" t="s" s="2">
+        <v>1214</v>
+      </c>
+      <c r="AH737" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI737" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ737" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK737" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="B738" t="s" s="2">
+        <v>1610</v>
+      </c>
+      <c r="C738" t="s" s="2">
+        <v>1611</v>
+      </c>
+      <c r="D738" s="2"/>
+      <c r="E738" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F738" s="2"/>
+      <c r="G738" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H738" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I738" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J738" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K738" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L738" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M738" t="s" s="2">
+        <v>1217</v>
+      </c>
+      <c r="N738" t="s" s="2">
+        <v>1218</v>
+      </c>
+      <c r="O738" s="2"/>
+      <c r="P738" t="s" s="2">
+        <v>1219</v>
+      </c>
+      <c r="Q738" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R738" s="2"/>
+      <c r="S738" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T738" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U738" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V738" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W738" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X738" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y738" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z738" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA738" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB738" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC738" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD738" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE738" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF738" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG738" t="s" s="2">
+        <v>1220</v>
+      </c>
+      <c r="AH738" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI738" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ738" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK738" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="B739" t="s" s="2">
+        <v>1612</v>
+      </c>
+      <c r="C739" t="s" s="2">
+        <v>1612</v>
+      </c>
+      <c r="D739" s="2"/>
+      <c r="E739" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F739" s="2"/>
+      <c r="G739" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H739" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I739" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J739" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K739" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L739" t="s" s="2">
+        <v>1072</v>
+      </c>
+      <c r="M739" t="s" s="2">
+        <v>1356</v>
+      </c>
+      <c r="N739" t="s" s="2">
+        <v>1357</v>
+      </c>
+      <c r="O739" t="s" s="2">
+        <v>1613</v>
+      </c>
+      <c r="P739" t="s" s="2">
+        <v>1113</v>
+      </c>
+      <c r="Q739" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R739" s="2"/>
+      <c r="S739" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T739" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U739" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V739" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W739" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X739" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y739" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z739" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA739" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB739" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC739" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD739" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE739" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF739" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG739" t="s" s="2">
+        <v>1612</v>
+      </c>
+      <c r="AH739" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI739" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ739" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK739" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="B740" t="s" s="2">
+        <v>1614</v>
+      </c>
+      <c r="C740" t="s" s="2">
+        <v>1614</v>
+      </c>
+      <c r="D740" s="2"/>
+      <c r="E740" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F740" s="2"/>
+      <c r="G740" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H740" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I740" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J740" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K740" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L740" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="M740" t="s" s="2">
+        <v>1226</v>
+      </c>
+      <c r="N740" t="s" s="2">
+        <v>1496</v>
+      </c>
+      <c r="O740" s="2"/>
+      <c r="P740" t="s" s="2">
+        <v>1615</v>
+      </c>
+      <c r="Q740" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R740" s="2"/>
+      <c r="S740" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T740" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U740" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V740" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W740" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X740" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y740" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="Z740" t="s" s="2">
+        <v>1230</v>
+      </c>
+      <c r="AA740" t="s" s="2">
+        <v>1231</v>
+      </c>
+      <c r="AB740" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC740" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD740" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE740" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF740" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG740" t="s" s="2">
+        <v>1614</v>
+      </c>
+      <c r="AH740" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI740" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ740" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK740" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="B741" t="s" s="2">
+        <v>1616</v>
+      </c>
+      <c r="C741" t="s" s="2">
+        <v>1616</v>
+      </c>
+      <c r="D741" s="2"/>
+      <c r="E741" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F741" s="2"/>
+      <c r="G741" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H741" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I741" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J741" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K741" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L741" t="s" s="2">
+        <v>1233</v>
+      </c>
+      <c r="M741" t="s" s="2">
+        <v>1617</v>
+      </c>
+      <c r="N741" t="s" s="2">
+        <v>1618</v>
+      </c>
+      <c r="O741" s="2"/>
+      <c r="P741" s="2"/>
+      <c r="Q741" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R741" s="2"/>
+      <c r="S741" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T741" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U741" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V741" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W741" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X741" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y741" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z741" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA741" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB741" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC741" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD741" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE741" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF741" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG741" t="s" s="2">
+        <v>1616</v>
+      </c>
+      <c r="AH741" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI741" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ741" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK741" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="B742" t="s" s="2">
+        <v>1619</v>
+      </c>
+      <c r="C742" t="s" s="2">
+        <v>1619</v>
+      </c>
+      <c r="D742" s="2"/>
+      <c r="E742" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F742" s="2"/>
+      <c r="G742" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H742" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I742" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J742" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K742" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L742" t="s" s="2">
+        <v>1080</v>
+      </c>
+      <c r="M742" t="s" s="2">
+        <v>1620</v>
+      </c>
+      <c r="N742" t="s" s="2">
+        <v>1621</v>
+      </c>
+      <c r="O742" s="2"/>
+      <c r="P742" t="s" s="2">
+        <v>1622</v>
+      </c>
+      <c r="Q742" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R742" s="2"/>
+      <c r="S742" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T742" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U742" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V742" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W742" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X742" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y742" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z742" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA742" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB742" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC742" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD742" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE742" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF742" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG742" t="s" s="2">
+        <v>1619</v>
+      </c>
+      <c r="AH742" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI742" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ742" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK742" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="B743" t="s" s="2">
+        <v>1623</v>
+      </c>
+      <c r="C743" t="s" s="2">
+        <v>1623</v>
+      </c>
+      <c r="D743" s="2"/>
+      <c r="E743" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F743" s="2"/>
+      <c r="G743" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H743" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I743" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J743" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K743" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L743" t="s" s="2">
+        <v>1332</v>
+      </c>
+      <c r="M743" t="s" s="2">
+        <v>1502</v>
+      </c>
+      <c r="N743" t="s" s="2">
+        <v>1503</v>
+      </c>
+      <c r="O743" s="2"/>
+      <c r="P743" t="s" s="2">
+        <v>1624</v>
+      </c>
+      <c r="Q743" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R743" s="2"/>
+      <c r="S743" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T743" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U743" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V743" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W743" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X743" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y743" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z743" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA743" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB743" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC743" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD743" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE743" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF743" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG743" t="s" s="2">
+        <v>1623</v>
+      </c>
+      <c r="AH743" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI743" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ743" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK743" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="B744" t="s" s="2">
+        <v>1625</v>
+      </c>
+      <c r="C744" t="s" s="2">
+        <v>1625</v>
+      </c>
+      <c r="D744" s="2"/>
+      <c r="E744" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F744" s="2"/>
+      <c r="G744" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H744" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I744" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J744" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K744" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L744" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M744" t="s" s="2">
+        <v>1626</v>
+      </c>
+      <c r="N744" t="s" s="2">
+        <v>1627</v>
+      </c>
+      <c r="O744" s="2"/>
+      <c r="P744" s="2"/>
+      <c r="Q744" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R744" s="2"/>
+      <c r="S744" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T744" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U744" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V744" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W744" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X744" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y744" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z744" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA744" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB744" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC744" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD744" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE744" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF744" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG744" t="s" s="2">
+        <v>1625</v>
+      </c>
+      <c r="AH744" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI744" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ744" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK744" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="B745" t="s" s="2">
+        <v>1628</v>
+      </c>
+      <c r="C745" t="s" s="2">
+        <v>1628</v>
+      </c>
+      <c r="D745" s="2"/>
+      <c r="E745" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F745" s="2"/>
+      <c r="G745" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H745" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I745" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J745" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K745" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L745" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M745" t="s" s="2">
+        <v>1629</v>
+      </c>
+      <c r="N745" t="s" s="2">
+        <v>1630</v>
+      </c>
+      <c r="O745" t="s" s="2">
+        <v>1631</v>
+      </c>
+      <c r="P745" t="s" s="2">
+        <v>1632</v>
+      </c>
+      <c r="Q745" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R745" s="2"/>
+      <c r="S745" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T745" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U745" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V745" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W745" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X745" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y745" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z745" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA745" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB745" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC745" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD745" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE745" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF745" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG745" t="s" s="2">
+        <v>1628</v>
+      </c>
+      <c r="AH745" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI745" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ745" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK745" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="B746" t="s" s="2">
+        <v>1633</v>
+      </c>
+      <c r="C746" t="s" s="2">
+        <v>1633</v>
+      </c>
+      <c r="D746" s="2"/>
+      <c r="E746" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F746" s="2"/>
+      <c r="G746" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H746" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I746" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J746" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K746" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L746" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M746" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="N746" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="O746" s="2"/>
+      <c r="P746" s="2"/>
+      <c r="Q746" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R746" s="2"/>
+      <c r="S746" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T746" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U746" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V746" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W746" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X746" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y746" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z746" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA746" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB746" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC746" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD746" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE746" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF746" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG746" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH746" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI746" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ746" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK746" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="B747" t="s" s="2">
+        <v>1634</v>
+      </c>
+      <c r="C747" t="s" s="2">
+        <v>1634</v>
+      </c>
+      <c r="D747" s="2"/>
+      <c r="E747" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F747" s="2"/>
+      <c r="G747" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H747" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I747" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J747" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K747" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L747" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="M747" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N747" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="O747" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="P747" s="2"/>
+      <c r="Q747" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R747" s="2"/>
+      <c r="S747" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T747" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U747" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V747" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W747" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X747" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y747" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z747" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA747" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB747" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC747" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD747" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE747" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF747" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG747" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH747" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI747" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ747" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK747" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="B748" t="s" s="2">
+        <v>1635</v>
+      </c>
+      <c r="C748" t="s" s="2">
+        <v>1635</v>
+      </c>
+      <c r="D748" s="2"/>
+      <c r="E748" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="F748" s="2"/>
+      <c r="G748" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H748" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I748" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J748" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="K748" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L748" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="M748" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="N748" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="O748" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="P748" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="Q748" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R748" s="2"/>
+      <c r="S748" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T748" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U748" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V748" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W748" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X748" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y748" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z748" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA748" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB748" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC748" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD748" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE748" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF748" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG748" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AH748" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI748" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ748" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK748" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="B749" t="s" s="2">
+        <v>1636</v>
+      </c>
+      <c r="C749" t="s" s="2">
+        <v>1636</v>
+      </c>
+      <c r="D749" s="2"/>
+      <c r="E749" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F749" s="2"/>
+      <c r="G749" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H749" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I749" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J749" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K749" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L749" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M749" t="s" s="2">
+        <v>1383</v>
+      </c>
+      <c r="N749" t="s" s="2">
+        <v>1384</v>
+      </c>
+      <c r="O749" t="s" s="2">
+        <v>1385</v>
+      </c>
+      <c r="P749" t="s" s="2">
+        <v>1386</v>
+      </c>
+      <c r="Q749" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R749" s="2"/>
+      <c r="S749" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T749" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U749" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V749" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W749" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X749" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y749" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="Z749" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AA749" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AB749" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC749" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD749" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE749" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF749" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG749" t="s" s="2">
+        <v>1636</v>
+      </c>
+      <c r="AH749" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI749" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ749" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK749" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="B750" t="s" s="2">
+        <v>1637</v>
+      </c>
+      <c r="C750" t="s" s="2">
+        <v>1637</v>
+      </c>
+      <c r="D750" s="2"/>
+      <c r="E750" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F750" s="2"/>
+      <c r="G750" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H750" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I750" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J750" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K750" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L750" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M750" t="s" s="2">
+        <v>1388</v>
+      </c>
+      <c r="N750" t="s" s="2">
+        <v>1389</v>
+      </c>
+      <c r="O750" t="s" s="2">
+        <v>1390</v>
+      </c>
+      <c r="P750" t="s" s="2">
+        <v>1391</v>
+      </c>
+      <c r="Q750" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R750" s="2"/>
+      <c r="S750" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T750" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U750" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V750" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W750" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X750" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y750" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z750" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA750" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB750" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC750" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD750" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE750" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF750" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG750" t="s" s="2">
+        <v>1637</v>
+      </c>
+      <c r="AH750" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI750" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ750" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK750" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="s" s="2">
+        <v>1638</v>
+      </c>
+      <c r="B751" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="C751" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="D751" s="2"/>
+      <c r="E751" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F751" s="2"/>
+      <c r="G751" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H751" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I751" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J751" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K751" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L751" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="M751" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="N751" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="O751" s="2"/>
+      <c r="P751" s="2"/>
+      <c r="Q751" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R751" s="2"/>
+      <c r="S751" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T751" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U751" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V751" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W751" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X751" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y751" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z751" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA751" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB751" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC751" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD751" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE751" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF751" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG751" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AH751" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI751" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ751" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK751" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="s" s="2">
+        <v>1638</v>
+      </c>
+      <c r="B752" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="C752" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D752" s="2"/>
+      <c r="E752" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F752" s="2"/>
+      <c r="G752" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H752" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I752" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J752" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K752" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L752" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M752" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="N752" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="O752" s="2"/>
+      <c r="P752" s="2"/>
+      <c r="Q752" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R752" s="2"/>
+      <c r="S752" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T752" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U752" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V752" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W752" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X752" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y752" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z752" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA752" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB752" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC752" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD752" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE752" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF752" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG752" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH752" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI752" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ752" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK752" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="s" s="2">
+        <v>1638</v>
+      </c>
+      <c r="B753" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C753" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="D753" s="2"/>
+      <c r="E753" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F753" s="2"/>
+      <c r="G753" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H753" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I753" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J753" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K753" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L753" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="M753" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N753" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="O753" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="P753" s="2"/>
+      <c r="Q753" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R753" s="2"/>
+      <c r="S753" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T753" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U753" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V753" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W753" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X753" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y753" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z753" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA753" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB753" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC753" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AD753" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AE753" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF753" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AG753" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH753" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI753" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ753" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK753" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="s" s="2">
+        <v>1638</v>
+      </c>
+      <c r="B754" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="C754" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="D754" s="2"/>
+      <c r="E754" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F754" s="2"/>
+      <c r="G754" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H754" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I754" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J754" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="K754" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L754" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="M754" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N754" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O754" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="P754" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="Q754" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R754" s="2"/>
+      <c r="S754" t="s" s="2">
+        <v>918</v>
+      </c>
+      <c r="T754" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U754" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V754" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W754" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X754" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y754" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="Z754" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AA754" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AB754" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC754" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD754" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE754" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF754" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG754" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AH754" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI754" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ754" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK754" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="s" s="2">
+        <v>1638</v>
+      </c>
+      <c r="B755" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="C755" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="D755" s="2"/>
+      <c r="E755" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F755" s="2"/>
+      <c r="G755" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H755" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I755" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J755" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K755" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L755" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M755" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="N755" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="O755" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="P755" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="Q755" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R755" s="2"/>
+      <c r="S755" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T755" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U755" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V755" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W755" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X755" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y755" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="Z755" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AA755" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AB755" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC755" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD755" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE755" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF755" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG755" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AH755" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI755" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ755" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK755" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="s" s="2">
+        <v>1638</v>
+      </c>
+      <c r="B756" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="C756" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="D756" s="2"/>
+      <c r="E756" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F756" s="2"/>
+      <c r="G756" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H756" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I756" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J756" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K756" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L756" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="M756" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N756" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="O756" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="P756" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="Q756" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R756" s="2"/>
+      <c r="S756" t="s" s="2">
+        <v>1643</v>
+      </c>
+      <c r="T756" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U756" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="V756" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W756" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X756" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y756" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z756" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA756" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB756" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC756" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD756" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE756" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF756" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG756" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AH756" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI756" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ756" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK756" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="s" s="2">
+        <v>1638</v>
+      </c>
+      <c r="B757" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="C757" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="D757" s="2"/>
+      <c r="E757" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F757" s="2"/>
+      <c r="G757" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H757" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I757" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J757" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K757" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L757" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M757" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="N757" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="O757" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="P757" s="2"/>
+      <c r="Q757" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R757" s="2"/>
+      <c r="S757" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T757" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U757" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="V757" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W757" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X757" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y757" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z757" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA757" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB757" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC757" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD757" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE757" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF757" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG757" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AH757" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI757" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ757" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK757" t="s" s="2">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="s" s="2">
+        <v>1638</v>
+      </c>
+      <c r="B758" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="C758" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="D758" s="2"/>
+      <c r="E758" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F758" s="2"/>
+      <c r="G758" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H758" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I758" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J758" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K758" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L758" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M758" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N758" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="O758" s="2"/>
+      <c r="P758" s="2"/>
+      <c r="Q758" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R758" s="2"/>
+      <c r="S758" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T758" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U758" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V758" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W758" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X758" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y758" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z758" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA758" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB758" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC758" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD758" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE758" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF758" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG758" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AH758" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI758" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ758" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK758" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="s" s="2">
+        <v>1638</v>
+      </c>
+      <c r="B759" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AH729" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI729" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ729" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK729" t="s" s="2">
+      <c r="C759" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="D759" s="2"/>
+      <c r="E759" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F759" s="2"/>
+      <c r="G759" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H759" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I759" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J759" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K759" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L759" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M759" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="N759" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="O759" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="P759" s="2"/>
+      <c r="Q759" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R759" s="2"/>
+      <c r="S759" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T759" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U759" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V759" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W759" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X759" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y759" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z759" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA759" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB759" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC759" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD759" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE759" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF759" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG759" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AH759" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI759" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ759" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK759" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="s" s="2">
+        <v>1645</v>
+      </c>
+      <c r="B760" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="C760" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="D760" s="2"/>
+      <c r="E760" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F760" s="2"/>
+      <c r="G760" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H760" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I760" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J760" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K760" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L760" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="M760" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="N760" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="O760" s="2"/>
+      <c r="P760" s="2"/>
+      <c r="Q760" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R760" s="2"/>
+      <c r="S760" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T760" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U760" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V760" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W760" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X760" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y760" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z760" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA760" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB760" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC760" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD760" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE760" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF760" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG760" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AH760" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI760" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ760" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK760" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="s" s="2">
+        <v>1645</v>
+      </c>
+      <c r="B761" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="C761" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D761" s="2"/>
+      <c r="E761" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F761" s="2"/>
+      <c r="G761" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H761" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I761" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J761" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K761" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L761" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M761" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="N761" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="O761" s="2"/>
+      <c r="P761" s="2"/>
+      <c r="Q761" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R761" s="2"/>
+      <c r="S761" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T761" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U761" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V761" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W761" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X761" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y761" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z761" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA761" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB761" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC761" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD761" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE761" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF761" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG761" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH761" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI761" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ761" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK761" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="s" s="2">
+        <v>1645</v>
+      </c>
+      <c r="B762" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C762" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="D762" s="2"/>
+      <c r="E762" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F762" s="2"/>
+      <c r="G762" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H762" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I762" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J762" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K762" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L762" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="M762" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N762" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="O762" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="P762" s="2"/>
+      <c r="Q762" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R762" s="2"/>
+      <c r="S762" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T762" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U762" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V762" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W762" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X762" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y762" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z762" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA762" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB762" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC762" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AD762" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AE762" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF762" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AG762" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH762" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI762" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ762" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK762" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="s" s="2">
+        <v>1645</v>
+      </c>
+      <c r="B763" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="C763" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="D763" s="2"/>
+      <c r="E763" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F763" s="2"/>
+      <c r="G763" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H763" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I763" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J763" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="K763" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L763" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="M763" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N763" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O763" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="P763" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="Q763" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R763" s="2"/>
+      <c r="S763" t="s" s="2">
+        <v>934</v>
+      </c>
+      <c r="T763" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U763" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V763" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W763" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X763" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y763" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="Z763" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AA763" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AB763" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC763" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD763" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE763" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF763" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG763" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AH763" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI763" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ763" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK763" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="s" s="2">
+        <v>1645</v>
+      </c>
+      <c r="B764" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="C764" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="D764" s="2"/>
+      <c r="E764" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F764" s="2"/>
+      <c r="G764" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H764" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I764" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J764" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K764" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L764" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M764" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="N764" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="O764" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="P764" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="Q764" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R764" s="2"/>
+      <c r="S764" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T764" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U764" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V764" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W764" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X764" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y764" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="Z764" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AA764" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AB764" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC764" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD764" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE764" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF764" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG764" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AH764" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI764" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ764" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK764" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="s" s="2">
+        <v>1645</v>
+      </c>
+      <c r="B765" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="C765" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="D765" s="2"/>
+      <c r="E765" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F765" s="2"/>
+      <c r="G765" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H765" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I765" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J765" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K765" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L765" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="M765" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N765" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="O765" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="P765" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="Q765" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R765" s="2"/>
+      <c r="S765" t="s" s="2">
+        <v>1650</v>
+      </c>
+      <c r="T765" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U765" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="V765" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W765" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X765" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y765" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z765" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA765" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB765" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC765" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD765" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE765" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF765" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG765" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AH765" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI765" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ765" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK765" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="s" s="2">
+        <v>1645</v>
+      </c>
+      <c r="B766" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="C766" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="D766" s="2"/>
+      <c r="E766" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F766" s="2"/>
+      <c r="G766" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H766" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I766" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J766" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K766" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L766" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M766" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="N766" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="O766" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="P766" s="2"/>
+      <c r="Q766" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R766" s="2"/>
+      <c r="S766" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T766" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U766" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="V766" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W766" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X766" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="Y766" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z766" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA766" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB766" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC766" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD766" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE766" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF766" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG766" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AH766" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI766" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ766" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK766" t="s" s="2">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="s" s="2">
+        <v>1645</v>
+      </c>
+      <c r="B767" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="C767" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="D767" s="2"/>
+      <c r="E767" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F767" s="2"/>
+      <c r="G767" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H767" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I767" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J767" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K767" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L767" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M767" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N767" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="O767" s="2"/>
+      <c r="P767" s="2"/>
+      <c r="Q767" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R767" s="2"/>
+      <c r="S767" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T767" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U767" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V767" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W767" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X767" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y767" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z767" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA767" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB767" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC767" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD767" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE767" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF767" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG767" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AH767" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI767" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ767" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK767" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="s" s="2">
+        <v>1645</v>
+      </c>
+      <c r="B768" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="C768" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="D768" s="2"/>
+      <c r="E768" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F768" s="2"/>
+      <c r="G768" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H768" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I768" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J768" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K768" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L768" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M768" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="N768" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="O768" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="P768" s="2"/>
+      <c r="Q768" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R768" s="2"/>
+      <c r="S768" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T768" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U768" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V768" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W768" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X768" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y768" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z768" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA768" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB768" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC768" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD768" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE768" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF768" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG768" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AH768" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI768" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ768" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK768" t="s" s="2">
         <v>103</v>
       </c>
     </row>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T06:34:41+00:00</t>
+    <t>2024-04-11T09:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-11T09:53:59+00:00</t>
+    <t>2024-04-12T06:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T06:23:14+00:00</t>
+    <t>2024-04-16T10:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-16T10:58:26+00:00</t>
+    <t>2024-04-18T15:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4523,7 +4523,7 @@
     <t>Patient.link.other</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:20:26+00:00</t>
+    <t>2024-04-18T15:27:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:27:51+00:00</t>
+    <t>2024-04-22T11:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T11:01:11+00:00</t>
+    <t>2024-04-22T12:03:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T12:03:36+00:00</t>
+    <t>2024-04-22T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T13:38:01+00:00</t>
+    <t>2024-04-23T08:24:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5134,7 +5134,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-min-digits-sor:SOR Identifiers are at minimum 11 digits long. See https://sundhedsdatastyrelsen.dk/-/media/sds/filer/rammer-og-retningslinjer/organisationsregistrering/adgang-til-sor/info-om-opbygningen-af-sor-ider.pdf {matches('^([0-9]){11,}$')}</t>
+min-digits-sor:SOR Identifiers are at minimum 11 digits long. See https://sundhedsdatastyrelsen.dk/da/rammer-og-retningslinjer/organisationsregistrering {matches('^([0-9]){11,}$')}</t>
   </si>
   <si>
     <t>dk-core-x-ecpr-identifier</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T08:24:27+00:00</t>
+    <t>2024-04-23T10:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T10:50:14+00:00</t>
+    <t>2024-04-23T18:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2968,7 +2968,7 @@
     <t>KombitOrgIdentifier</t>
   </si>
   <si>
-    <t>Kombit Org Identifier</t>
+    <t>Kombit Organsation Identifier</t>
   </si>
   <si>
     <t>Identifier holding the organization code issued by KOMBIT</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T18:15:55+00:00</t>
+    <t>2024-05-02T12:47:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -31814,7 +31814,7 @@
         <v>77</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AK220" t="s" s="2">
         <v>80</v>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-02T12:47:39+00:00</t>
+    <t>2024-05-03T13:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T06:35:09+00:00</t>
+    <t>2024-05-06T07:49:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T09:45:49+00:00</t>
+    <t>2024-05-12T11:37:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T12:49:28+00:00</t>
+    <t>2024-11-15T13:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T13:03:47+00:00</t>
+    <t>2024-11-29T07:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T07:41:39+00:00</t>
+    <t>2024-11-29T10:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T10:20:07+00:00</t>
+    <t>2024-12-11T08:38:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:09:03+00:00</t>
+    <t>2024-12-16T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:16:17+00:00</t>
+    <t>2024-12-16T15:31:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
